--- a/InputData/indst/WHRPbI/Waste Heat Recovery Potl by Indst.xlsx
+++ b/InputData/indst/WHRPbI/Waste Heat Recovery Potl by Indst.xlsx
@@ -1,22 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr autoCompressPictures="0" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanO'Brien\Models\EPS\US\eps-us\InputData\indst\WHRPbI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\indst\WHRPbI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2328D90-1737-4CD1-BA3B-E386F2BD6510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87205B78-6E0D-493E-B94C-845DC7BFEC91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="770" xr2:uid="{7D5963C0-FA73-4A20-914D-C5C19178119F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="770" xr2:uid="{7D5963C0-FA73-4A20-914D-C5C19178119F}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="EU Data" sheetId="149" r:id="rId2"/>
-    <sheet name="WHRPbI" sheetId="148" r:id="rId3"/>
+    <sheet name="BPFUbIP-Summed Data by Industry" sheetId="150" r:id="rId3"/>
+    <sheet name="Calcs" sheetId="151" r:id="rId4"/>
+    <sheet name="WHRPbI" sheetId="148" r:id="rId5"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId6"/>
+    <externalReference r:id="rId7"/>
+    <externalReference r:id="rId8"/>
+    <externalReference r:id="rId9"/>
+  </externalReferences>
+  <definedNames>
+    <definedName name="CH4_to_CO2e">'[1]Cross-Page Data'!$C$12</definedName>
+    <definedName name="cpi_2010to2012">#REF!</definedName>
+    <definedName name="cpi_2013to2012">#REF!</definedName>
+    <definedName name="cpi_2014to2012">#REF!</definedName>
+    <definedName name="cpi_2016to2012">#REF!</definedName>
+    <definedName name="gigwatts_to_megawatts">[3]About!$A$31</definedName>
+    <definedName name="N2O_to_CO2e">'[1]Cross-Page Data'!$C$13</definedName>
+    <definedName name="unit_conv">[4]About!$A$123</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -31,8 +49,66 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Dan O'Brien</author>
+  </authors>
+  <commentList>
+    <comment ref="C4" authorId="0" shapeId="0" xr:uid="{0A39BB56-A820-4667-9208-6977F04070CC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Dan O'Brien:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+added to enable financial policies driving boiler electrification</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J4" authorId="0" shapeId="0" xr:uid="{D8CE2B53-D090-49AE-BD7D-34621527F252}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Dan O'Brien:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+added to enable financial policies driving boiler electrification</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="121">
   <si>
     <t>Sources:</t>
   </si>
@@ -196,18 +272,217 @@
     <t>dmnl</t>
   </si>
   <si>
-    <t>EPS ISIC</t>
+    <t>Fuel Type</t>
+  </si>
+  <si>
+    <t>electricity if</t>
+  </si>
+  <si>
+    <t>heavy or residual fuel oil if</t>
+  </si>
+  <si>
+    <t>petroleum diesel if</t>
+  </si>
+  <si>
+    <t>natural gas if</t>
+  </si>
+  <si>
+    <t>LPG propane or butane if</t>
+  </si>
+  <si>
+    <t>hard coal if</t>
+  </si>
+  <si>
+    <t>biomass if</t>
+  </si>
+  <si>
+    <t>MECS Row Adder</t>
+  </si>
+  <si>
+    <t>MECS/Non-MECS</t>
+  </si>
+  <si>
+    <t>Industry Category</t>
+  </si>
+  <si>
+    <t>Boilers</t>
+  </si>
+  <si>
+    <t>Nonboiler heat</t>
+  </si>
+  <si>
+    <t>Cooling</t>
+  </si>
+  <si>
+    <t>Machine Drive</t>
+  </si>
+  <si>
+    <t>Other process</t>
+  </si>
+  <si>
+    <t>Facility HVAC</t>
+  </si>
+  <si>
+    <t>Facility Lighting</t>
+  </si>
+  <si>
+    <t>Other Nonprocess</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>uses non-MECS EIA table</t>
+  </si>
+  <si>
+    <t>Buildings is assumed to be heating for barns and greenhouses, which is process heating, not non-process heating, when it is for animals or plants in agriculture.  IRR = irrigation, which is assumed to be machine drive (for pumps). Also, we count municipal solid waste (which is not broken out as an industrial fuel in the EPS) as biomass.</t>
+  </si>
+  <si>
+    <t>Electricity and diesel use are assumed to be machine drive (mining equipment, elevators, pumps, etc.)  Natural gas is assumed to provide process heat.</t>
+  </si>
+  <si>
+    <t>Electricity and diesel use are assumed to be machine drive (mining equipment, elevators, pumps, etc.)  Other fuels are assumed to provide process heat.</t>
+  </si>
+  <si>
+    <t>MECS</t>
+  </si>
+  <si>
+    <t>For biomass, we assume energy use is split evenly between boilers and non-boiler process heating (such as drying).</t>
+  </si>
+  <si>
+    <t>see notes below</t>
+  </si>
+  <si>
+    <t>The energy here is assumed to be largely pipelines, not natural gas processing.  Energy use is dominated by pumps to move fluid, which is machine drive.</t>
+  </si>
+  <si>
+    <t>See notes below on this sheet.</t>
+  </si>
+  <si>
+    <t>Electricity and diesel use are assumed to be machine drive (construction equipment).  Other fuels are assumed to provide process heat.</t>
+  </si>
+  <si>
+    <t>Note on MECS Rows / Categories</t>
+  </si>
+  <si>
+    <t>In cases where the EPS industry category is the sum of several MECS categories, we just take the most representative and/or largest MECS category,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note: "other nonprocess" covers several categories, as you can see in Table 5.2: in MECS, it sums </t>
+  </si>
+  <si>
+    <t>which simplifies the formulas greatly and shouldn't meaningfully affect the results, as all we care about here are the percentages of energy use by industrial process,</t>
+  </si>
+  <si>
+    <t>onsite transportation, facility support, and onsite electricity generation (e.g., generators).</t>
+  </si>
+  <si>
+    <t>not the total quantities of energy use.</t>
+  </si>
+  <si>
+    <t>For non-manufacturing industries, the biggest contributor is mobile equipment like agricultural</t>
+  </si>
+  <si>
+    <t>Note on Excluded Energy Uses</t>
+  </si>
+  <si>
+    <t>tractors, offroad construction equipment and mobile mining equipment. The file indst/PoONEUTiMEbIC</t>
+  </si>
+  <si>
+    <t>Nonprocess uses (building HVAC, on-site vehicles like farm vehicles and forklifts) are omitted.</t>
+  </si>
+  <si>
+    <t>defines the share of other nonprocess equipment is mobile equipment. This is important because</t>
+  </si>
+  <si>
+    <t>Heating barns and greenhouses to grow animals and plants is considered a process use, not a non-process use, even though it is heating of buildings.</t>
+  </si>
+  <si>
+    <t>both the technologies and policies for decarbonizing as well as the costs of these sources are quite</t>
+  </si>
+  <si>
+    <t>different from stationary equipment.</t>
+  </si>
+  <si>
+    <t>Note on Water and Waste Industry</t>
+  </si>
+  <si>
+    <t>Solid waste is dominated by vehicles (waste hauling trucks), which are considered nonprocess uses and are excluded.</t>
+  </si>
+  <si>
+    <t>Water treatment is mostly electricity, but fossil fuels are sometimes used for multi-effect distillation and flash distillation,</t>
+  </si>
+  <si>
+    <t>both of which involve boiling water.  Since the fuel is being used to boil water, we categorize it as "boilers," even if the</t>
+  </si>
+  <si>
+    <t>equipment involved may not techically be a "boiler."</t>
+  </si>
+  <si>
+    <t>See Figure 8 on page 28 of the IEA Water-Energy Nexus report (2016) and the "Thermal" explanation on page 36, at:</t>
+  </si>
+  <si>
+    <t>https://iea.blob.core.windows.net/assets/e4a7e1a5-b6ed-4f36-911f-b0111e49aab9/WorldEnergyOutlook2016ExcerptWaterEnergyNexus.pdf</t>
+  </si>
+  <si>
+    <t>We arbitrarily assign "1" to boilers and "0" to other rows to achieve a 100% value for boilers.</t>
+  </si>
+  <si>
+    <t>For electricity, energy use is dominated by pumping and water transfer, which is machine drive, and even treatment steps use electricity for machine drive.</t>
+  </si>
+  <si>
+    <t>industry share of energy used for heat</t>
+  </si>
+  <si>
+    <t>Share of industry energy use for heat</t>
+  </si>
+  <si>
+    <t>indst/BPFUbIP</t>
+  </si>
+  <si>
+    <t>We find the potential recoverable waste heat from Bianchi et al. This source provides</t>
+  </si>
+  <si>
+    <t>Rather than attempting to map temperature data from the Bianchi paper, which would</t>
+  </si>
+  <si>
+    <t>recovery potential as a share of total industry primary energy consumption. We</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the input file indst/BPFUbIP. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">convert this to each industry's share of energy used to generate heat via data found in </t>
+  </si>
+  <si>
+    <t xml:space="preserve">be difficult because we separate heat demand between boilers and nonboiler heat at </t>
+  </si>
+  <si>
+    <t>various temperatures, we simply assume that recoverable heat is distributed proportionally</t>
+  </si>
+  <si>
+    <t xml:space="preserve">to each industry's demand for boiler and nonboiler heat of various temperatures. </t>
+  </si>
+  <si>
+    <t>EPS ISIC 1</t>
+  </si>
+  <si>
+    <t>EPS ISIC 2</t>
+  </si>
+  <si>
+    <t>EPS ISIC 3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="170" formatCode="0.0000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="33" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -417,8 +692,37 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -607,6 +911,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -825,7 +1147,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="106">
+  <cellStyleXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyProtection="0">
       <alignment wrapText="1"/>
@@ -996,8 +1318,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1012,9 +1335,42 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="18" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="18" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="18" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="106" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="106">
+  <cellStyles count="107">
     <cellStyle name="20% - Accent1" xfId="43" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent1 2" xfId="68" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="20% - Accent2" xfId="46" builtinId="34" customBuiltin="1"/>
@@ -1085,6 +1441,7 @@
     <cellStyle name="Heading 3" xfId="29" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Heading 4" xfId="30" builtinId="19" customBuiltin="1"/>
     <cellStyle name="Hyperlink" xfId="9" builtinId="8" customBuiltin="1"/>
+    <cellStyle name="Hyperlink 2" xfId="106" xr:uid="{86C87D9E-AD21-4FCE-A226-2C057D1DA2B9}"/>
     <cellStyle name="Input" xfId="33" builtinId="20" customBuiltin="1"/>
     <cellStyle name="Linked Cell" xfId="36" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral 2" xfId="60" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
@@ -1183,8 +1540,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>420097</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>149164</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>162400</xdr:rowOff>
     </xdr:to>
@@ -1220,6 +1577,268 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="About"/>
+      <sheetName val="Cross-Page Data"/>
+      <sheetName val="Non-Energy FF CO2 Emissions"/>
+      <sheetName val="Cement CO2 Emissions"/>
+      <sheetName val="Iron and Steel"/>
+      <sheetName val="Coal Mining"/>
+      <sheetName val="Natural Gas Systems"/>
+      <sheetName val="Petroleum Systems"/>
+      <sheetName val="Chem - HCFC 22 Production"/>
+      <sheetName val="Chem - ODS"/>
+      <sheetName val="Other - Aluminum"/>
+      <sheetName val="Other - Magnesium"/>
+      <sheetName val="Other - Semiconductor Mfg"/>
+      <sheetName val="Other - Elec Trans and Dist"/>
+      <sheetName val="Agriculture - EF &amp; Manure Mgmt"/>
+      <sheetName val="Agriculture - Rice Cultivation"/>
+      <sheetName val="Agriculture - Soil Mgmt"/>
+      <sheetName val="Waste - Landfills"/>
+      <sheetName val="Waste - Water Treatment"/>
+      <sheetName val="Other Industrial Processes"/>
+      <sheetName val="Combined Data"/>
+      <sheetName val="BPEiC-CO2"/>
+      <sheetName val="BPEiC-CH4"/>
+      <sheetName val="BPEiC-N2O"/>
+      <sheetName val="BPEiC-F-gases"/>
+      <sheetName val="EPA (2017) Table A3.6-1"/>
+      <sheetName val="EPA (2017) Table A3.6-7"/>
+      <sheetName val="EPA (2017) Table A3.6-10"/>
+      <sheetName val="AEO 2017_Table 6"/>
+      <sheetName val="AEO 2017_Table 11"/>
+      <sheetName val="AEO 2017_Table 13"/>
+      <sheetName val="AEO 2017_Table 15"/>
+      <sheetName val="AEO 2017_Table 19"/>
+      <sheetName val="AEO 2017_Table 20"/>
+      <sheetName val="AEO 2017_Table 24"/>
+      <sheetName val="AEO 2017_Table 62"/>
+      <sheetName val="AEO 2016_Table 6"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="12">
+          <cell r="C12">
+            <v>28</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="C13">
+            <v>265</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9">
+        <row r="5">
+          <cell r="A5" t="str">
+            <v>Transport Refrigeration</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
+      <sheetData sheetId="26"/>
+      <sheetData sheetId="27"/>
+      <sheetData sheetId="28"/>
+      <sheetData sheetId="29"/>
+      <sheetData sheetId="30"/>
+      <sheetData sheetId="31"/>
+      <sheetData sheetId="32"/>
+      <sheetData sheetId="33"/>
+      <sheetData sheetId="34"/>
+      <sheetData sheetId="35"/>
+      <sheetData sheetId="36"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="About"/>
+      <sheetName val="EIA Requested Industry table"/>
+      <sheetName val="Ag-Forestry"/>
+      <sheetName val="Mobile vs Stationary"/>
+      <sheetName val="Table 5.2_old"/>
+      <sheetName val="mapping"/>
+      <sheetName val="Table 5.2"/>
+      <sheetName val="Table5_2_long"/>
+      <sheetName val="Summed Data by Industry"/>
+      <sheetName val="Raw Temperature Breakdown"/>
+      <sheetName val="Temps Mapped to EPS Industries"/>
+      <sheetName val="BPFUbIP-electricity"/>
+      <sheetName val="BPFUbIP-hard-coal"/>
+      <sheetName val="BPFUbIP-natural-gas"/>
+      <sheetName val="BPFUbIP-biomass"/>
+      <sheetName val="BPFUbIP-petroleum-diesel"/>
+      <sheetName val="BPFUbIP-heat"/>
+      <sheetName val="BPFUbIP-crude-oil"/>
+      <sheetName val="BPFUbIP-hvy-resid-fuel-oil"/>
+      <sheetName val="BPFUbIP-LPG"/>
+      <sheetName val="BPFUbIP-hydrogen"/>
+      <sheetName val="BPFUbIP-green-hydrogen"/>
+      <sheetName val="BPFUbIP-lowcarbon-hydrogen"/>
+      <sheetName val="BPFUbIP-fallback"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="About"/>
+      <sheetName val="2035 Report Deployment"/>
+      <sheetName val="2035 Report Data"/>
+      <sheetName val="EPS Output"/>
+      <sheetName val="AEO Table 9"/>
+      <sheetName val="AEO Table 9 (2019)"/>
+      <sheetName val="AEO Table 16"/>
+      <sheetName val="BGBSC"/>
+      <sheetName val="PAGBSC"/>
+      <sheetName val="SYGBSC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="31">
+          <cell r="A31">
+            <v>1000</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="About"/>
+      <sheetName val="Country Selector"/>
+      <sheetName val="Multipliers and Adjustments"/>
+      <sheetName val="EPA Data"/>
+      <sheetName val="Tech to Policy Mapping"/>
+      <sheetName val="SNAP Adjustment"/>
+      <sheetName val="Cement Data"/>
+      <sheetName val="Data Check"/>
+      <sheetName val="PERAC-cement"/>
+      <sheetName val="PERAC-ngps-mthncptr"/>
+      <sheetName val="PERAC-ngps-mthndstr"/>
+      <sheetName val="PERAC-fgassubstitution"/>
+      <sheetName val="PERAC-fgasdestruction"/>
+      <sheetName val="PERAC-fgasrecovery"/>
+      <sheetName val="PERAC-inspctmaintretrofit"/>
+      <sheetName val="PERAC-coalmining-mthncptr"/>
+      <sheetName val="PERAC-coalmining-mthndstr"/>
+      <sheetName val="PERAC-waste-mthncptr"/>
+      <sheetName val="PERAC-waste-mthndstr"/>
+      <sheetName val="PERAC-cropsrice"/>
+      <sheetName val="PERAC-livestock"/>
+      <sheetName val="PERAC-MCD"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="123">
+          <cell r="A123">
+            <v>1000000000000</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1509,24 +2128,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D27"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="76.5703125" customWidth="1"/>
-    <col min="3" max="3" width="5.140625" customWidth="1"/>
-    <col min="4" max="4" width="57.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="60.42578125" customWidth="1"/>
+    <col min="2" max="2" width="76.54296875" customWidth="1"/>
+    <col min="3" max="3" width="5.1796875" customWidth="1"/>
+    <col min="4" max="4" width="57.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="60.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1534,62 +2153,101 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B6" s="5">
         <v>2019</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B11" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B13" s="5"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D12" s="4"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D13" s="4"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D14" s="4"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D15" s="4"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D16" s="4"/>
-    </row>
-    <row r="17" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D17" s="4"/>
-    </row>
-    <row r="18" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D18" s="3"/>
-    </row>
-    <row r="19" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>110</v>
+      </c>
+      <c r="D18" s="4"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>112</v>
+      </c>
       <c r="D19" s="4"/>
     </row>
-    <row r="20" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D20" s="3"/>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>114</v>
+      </c>
+      <c r="D20" s="4"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>113</v>
+      </c>
+      <c r="D21" s="4"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D22" s="4"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D23" s="4"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>111</v>
+      </c>
+      <c r="D24" s="3"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>115</v>
+      </c>
+      <c r="D25" s="4"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>116</v>
+      </c>
+      <c r="D26" s="3"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>117</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1605,13 +2263,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54D27B78-5F3A-4024-A428-861147EC67D3}">
   <dimension ref="B22:J35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="38.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="43.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="34.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B22" s="6" t="s">
         <v>8</v>
       </c>
@@ -1631,10 +2292,16 @@
         <v>12</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>13</v>
       </c>
@@ -1663,7 +2330,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>14</v>
       </c>
@@ -1686,7 +2353,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
         <v>15</v>
       </c>
@@ -1709,7 +2376,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
         <v>16</v>
       </c>
@@ -1738,7 +2405,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>17</v>
       </c>
@@ -1764,7 +2431,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>18</v>
       </c>
@@ -1787,7 +2454,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>19</v>
       </c>
@@ -1810,7 +2477,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
         <v>20</v>
       </c>
@@ -1833,7 +2500,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B31" t="s">
         <v>21</v>
       </c>
@@ -1856,7 +2523,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
         <v>22</v>
       </c>
@@ -1882,7 +2549,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
         <v>23</v>
       </c>
@@ -1905,7 +2572,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B34" t="s">
         <v>24</v>
       </c>
@@ -1928,7 +2595,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B35" t="s">
         <v>25</v>
       </c>
@@ -1958,17 +2625,4316 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABA905B4-46CC-4EF4-952C-CB997603B4DF}">
+  <dimension ref="A1:BN47"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14" style="5" customWidth="1"/>
+    <col min="2" max="2" width="48.453125" customWidth="1"/>
+    <col min="3" max="10" width="16.1796875" customWidth="1"/>
+    <col min="11" max="11" width="6.7265625" customWidth="1"/>
+    <col min="12" max="19" width="16.1796875" customWidth="1"/>
+    <col min="20" max="20" width="6.7265625" customWidth="1"/>
+    <col min="21" max="28" width="16.1796875" customWidth="1"/>
+    <col min="29" max="29" width="6.7265625" customWidth="1"/>
+    <col min="30" max="37" width="16.1796875" customWidth="1"/>
+    <col min="38" max="38" width="6.7265625" customWidth="1"/>
+    <col min="39" max="46" width="16.1796875" customWidth="1"/>
+    <col min="47" max="47" width="6.7265625" customWidth="1"/>
+    <col min="48" max="55" width="16.1796875" customWidth="1"/>
+    <col min="56" max="56" width="6.7265625" customWidth="1"/>
+    <col min="57" max="64" width="16.1796875" customWidth="1"/>
+    <col min="65" max="65" width="6.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:66" x14ac:dyDescent="0.35">
+      <c r="B1" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L1" t="s">
+        <v>56</v>
+      </c>
+      <c r="M1" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1" t="s">
+        <v>56</v>
+      </c>
+      <c r="O1" t="s">
+        <v>56</v>
+      </c>
+      <c r="P1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>56</v>
+      </c>
+      <c r="R1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S1" t="s">
+        <v>56</v>
+      </c>
+      <c r="U1" t="s">
+        <v>57</v>
+      </c>
+      <c r="V1" t="s">
+        <v>57</v>
+      </c>
+      <c r="W1" t="s">
+        <v>57</v>
+      </c>
+      <c r="X1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:66" x14ac:dyDescent="0.35">
+      <c r="B2" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>8</v>
+      </c>
+      <c r="E2">
+        <v>9</v>
+      </c>
+      <c r="F2">
+        <v>10</v>
+      </c>
+      <c r="G2">
+        <v>11</v>
+      </c>
+      <c r="H2">
+        <v>12</v>
+      </c>
+      <c r="L2">
+        <v>4</v>
+      </c>
+      <c r="M2">
+        <v>8</v>
+      </c>
+      <c r="N2">
+        <v>9</v>
+      </c>
+      <c r="O2">
+        <v>10</v>
+      </c>
+      <c r="P2">
+        <v>11</v>
+      </c>
+      <c r="Q2">
+        <v>12</v>
+      </c>
+      <c r="U2">
+        <v>4</v>
+      </c>
+      <c r="V2">
+        <v>8</v>
+      </c>
+      <c r="W2">
+        <v>9</v>
+      </c>
+      <c r="X2">
+        <v>10</v>
+      </c>
+      <c r="Y2">
+        <v>11</v>
+      </c>
+      <c r="Z2">
+        <v>12</v>
+      </c>
+      <c r="AD2">
+        <v>4</v>
+      </c>
+      <c r="AE2">
+        <v>8</v>
+      </c>
+      <c r="AF2">
+        <v>9</v>
+      </c>
+      <c r="AG2">
+        <v>10</v>
+      </c>
+      <c r="AH2">
+        <v>11</v>
+      </c>
+      <c r="AI2">
+        <v>12</v>
+      </c>
+      <c r="AM2">
+        <v>4</v>
+      </c>
+      <c r="AN2">
+        <v>8</v>
+      </c>
+      <c r="AO2">
+        <v>9</v>
+      </c>
+      <c r="AP2">
+        <v>10</v>
+      </c>
+      <c r="AQ2">
+        <v>11</v>
+      </c>
+      <c r="AR2">
+        <v>12</v>
+      </c>
+      <c r="AV2">
+        <v>4</v>
+      </c>
+      <c r="AW2">
+        <v>8</v>
+      </c>
+      <c r="AX2">
+        <v>9</v>
+      </c>
+      <c r="AY2">
+        <v>10</v>
+      </c>
+      <c r="AZ2">
+        <v>11</v>
+      </c>
+      <c r="BA2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:66" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="L3" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="M3" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="N3" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="O3" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="P3" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q3" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="R3" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="S3" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="U3" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="V3" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="W3" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="X3" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y3" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z3" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA3" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB3" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AD3" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE3" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF3" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="AG3" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="AH3" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="AI3" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ3" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="AK3" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AM3" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN3" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="AO3" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="AP3" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="AQ3" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="AR3" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AS3" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="AT3" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AV3" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="AW3" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="AX3" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="AY3" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="AZ3" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="BA3" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="BB3" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="BC3" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="BE3" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="BF3" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="BG3" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="BH3" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="BI3" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ3" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="BK3" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="BL3" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="BN3" s="13" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:66" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="D4" s="15">
+        <v>32.676380000000002</v>
+      </c>
+      <c r="E4" s="15">
+        <v>11.53284</v>
+      </c>
+      <c r="F4" s="15">
+        <v>94.367660000000001</v>
+      </c>
+      <c r="H4" s="15">
+        <v>63.43061999999999</v>
+      </c>
+      <c r="I4" s="15">
+        <v>48.0535</v>
+      </c>
+      <c r="J4" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="L4" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15"/>
+      <c r="R4" s="15"/>
+      <c r="S4" s="15"/>
+      <c r="U4" s="15">
+        <v>19.144649999999999</v>
+      </c>
+      <c r="V4" s="15">
+        <v>19.144649999999999</v>
+      </c>
+      <c r="W4" s="15"/>
+      <c r="X4" s="15"/>
+      <c r="Y4" s="15"/>
+      <c r="Z4" s="15">
+        <v>19.144649999999999</v>
+      </c>
+      <c r="AA4" s="15"/>
+      <c r="AB4" s="17">
+        <v>533.56404999999995</v>
+      </c>
+      <c r="AD4" s="16">
+        <v>22.13025</v>
+      </c>
+      <c r="AE4" s="15">
+        <v>43.860500000000002</v>
+      </c>
+      <c r="AF4" s="15"/>
+      <c r="AG4" s="15">
+        <v>20.942</v>
+      </c>
+      <c r="AH4" s="15"/>
+      <c r="AI4" s="15">
+        <v>21.930250000000001</v>
+      </c>
+      <c r="AJ4" s="15"/>
+      <c r="AK4" s="15">
+        <v>3.8719999999999999</v>
+      </c>
+      <c r="AM4" s="15">
+        <v>15.014749999999999</v>
+      </c>
+      <c r="AN4" s="15">
+        <v>30.029499999999999</v>
+      </c>
+      <c r="AO4" s="15"/>
+      <c r="AP4" s="15">
+        <v>1.494</v>
+      </c>
+      <c r="AR4" s="15">
+        <v>30.029499999999999</v>
+      </c>
+      <c r="AS4" s="15"/>
+      <c r="AT4" s="15">
+        <v>6.1970000000000001</v>
+      </c>
+      <c r="AV4" s="18"/>
+      <c r="AW4" s="15"/>
+      <c r="AX4" s="15"/>
+      <c r="AY4" s="15"/>
+      <c r="AZ4" s="15"/>
+      <c r="BA4" s="15"/>
+      <c r="BB4" s="15"/>
+      <c r="BC4" s="15"/>
+      <c r="BE4" s="15">
+        <v>48.2</v>
+      </c>
+      <c r="BF4" s="15">
+        <v>154.173</v>
+      </c>
+      <c r="BG4" s="15"/>
+      <c r="BH4" s="15"/>
+      <c r="BI4" s="15"/>
+      <c r="BJ4" s="15"/>
+      <c r="BK4" s="15"/>
+      <c r="BL4" s="15"/>
+      <c r="BN4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:66" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="18"/>
+      <c r="F5" s="15">
+        <v>14.582999999999998</v>
+      </c>
+      <c r="H5" s="15">
+        <v>4.8610000000000007</v>
+      </c>
+      <c r="I5" s="15">
+        <v>4.8610000000000007</v>
+      </c>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="15"/>
+      <c r="R5" s="15"/>
+      <c r="S5" s="15"/>
+      <c r="U5" s="15"/>
+      <c r="V5" s="15"/>
+      <c r="W5" s="15"/>
+      <c r="X5" s="15"/>
+      <c r="Y5" s="15"/>
+      <c r="AA5" s="15"/>
+      <c r="AB5" s="17">
+        <v>57.362999999999992</v>
+      </c>
+      <c r="AD5" s="15"/>
+      <c r="AF5" s="15"/>
+      <c r="AG5" s="15"/>
+      <c r="AH5" s="15"/>
+      <c r="AI5" s="15">
+        <v>13.858000000000001</v>
+      </c>
+      <c r="AJ5" s="15"/>
+      <c r="AK5" s="15"/>
+      <c r="AM5" s="15"/>
+      <c r="AN5" s="15"/>
+      <c r="AO5" s="15"/>
+      <c r="AP5" s="15"/>
+      <c r="AQ5" s="15"/>
+      <c r="AR5" s="15"/>
+      <c r="AS5" s="15"/>
+      <c r="AT5" s="15"/>
+      <c r="AV5" s="15"/>
+      <c r="AW5" s="15"/>
+      <c r="AX5" s="15"/>
+      <c r="AY5" s="15"/>
+      <c r="AZ5" s="15"/>
+      <c r="BA5" s="15"/>
+      <c r="BB5" s="15"/>
+      <c r="BC5" s="15"/>
+      <c r="BE5" s="15"/>
+      <c r="BF5" s="15"/>
+      <c r="BG5" s="15"/>
+      <c r="BH5" s="15"/>
+      <c r="BI5" s="15"/>
+      <c r="BJ5" s="15"/>
+      <c r="BK5" s="15"/>
+      <c r="BL5" s="15"/>
+      <c r="BN5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:66" x14ac:dyDescent="0.35">
+      <c r="A6" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="18"/>
+      <c r="F6" s="15">
+        <v>76.234200000000001</v>
+      </c>
+      <c r="H6" s="15">
+        <v>25.4114</v>
+      </c>
+      <c r="I6" s="15">
+        <v>25.4114</v>
+      </c>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15">
+        <v>9.4600000000000009</v>
+      </c>
+      <c r="P6" s="15"/>
+      <c r="Q6" s="15"/>
+      <c r="R6" s="15"/>
+      <c r="S6" s="15"/>
+      <c r="U6" s="15"/>
+      <c r="V6" s="15"/>
+      <c r="W6" s="15"/>
+      <c r="Y6" s="15"/>
+      <c r="Z6" s="15"/>
+      <c r="AA6" s="15"/>
+      <c r="AB6" s="17">
+        <v>169.648</v>
+      </c>
+      <c r="AD6" s="15">
+        <v>101.6</v>
+      </c>
+      <c r="AE6" s="15">
+        <v>271.51499999999999</v>
+      </c>
+      <c r="AF6" s="15"/>
+      <c r="AG6" s="15"/>
+      <c r="AH6" s="15"/>
+      <c r="AI6" s="15"/>
+      <c r="AJ6" s="15"/>
+      <c r="AK6" s="15"/>
+      <c r="AM6" s="15"/>
+      <c r="AN6" s="15"/>
+      <c r="AO6" s="15"/>
+      <c r="AP6" s="15"/>
+      <c r="AQ6" s="15"/>
+      <c r="AR6" s="15"/>
+      <c r="AS6" s="15"/>
+      <c r="AT6" s="15"/>
+      <c r="AV6" s="15"/>
+      <c r="AW6" s="16">
+        <v>0.16</v>
+      </c>
+      <c r="AX6" s="15"/>
+      <c r="AY6" s="15"/>
+      <c r="AZ6" s="15"/>
+      <c r="BA6" s="15"/>
+      <c r="BB6" s="15"/>
+      <c r="BC6" s="15"/>
+      <c r="BE6" s="15"/>
+      <c r="BF6" s="15">
+        <v>8.6010000000000009</v>
+      </c>
+      <c r="BG6" s="15"/>
+      <c r="BH6" s="15"/>
+      <c r="BI6" s="15"/>
+      <c r="BJ6" s="15"/>
+      <c r="BK6" s="15"/>
+      <c r="BL6" s="15"/>
+      <c r="BN6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:66" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="18"/>
+      <c r="F7" s="15">
+        <v>66.2286</v>
+      </c>
+      <c r="H7" s="15">
+        <v>22.0762</v>
+      </c>
+      <c r="I7" s="15">
+        <v>22.0762</v>
+      </c>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="15"/>
+      <c r="O7" s="15"/>
+      <c r="P7" s="15"/>
+      <c r="Q7" s="15"/>
+      <c r="R7" s="15"/>
+      <c r="S7" s="15"/>
+      <c r="U7" s="15"/>
+      <c r="V7" s="15"/>
+      <c r="W7" s="15"/>
+      <c r="X7" s="15"/>
+      <c r="Y7" s="15"/>
+      <c r="AA7" s="15"/>
+      <c r="AB7" s="17">
+        <v>124.51900000000001</v>
+      </c>
+      <c r="AD7" s="15">
+        <v>10.7</v>
+      </c>
+      <c r="AE7" s="15">
+        <v>195.63399999999999</v>
+      </c>
+      <c r="AF7" s="15"/>
+      <c r="AG7" s="15"/>
+      <c r="AH7" s="15"/>
+      <c r="AI7" s="15"/>
+      <c r="AJ7" s="15"/>
+      <c r="AK7" s="15"/>
+      <c r="AM7" s="15"/>
+      <c r="AN7" s="15"/>
+      <c r="AO7" s="15"/>
+      <c r="AP7" s="15"/>
+      <c r="AQ7" s="15"/>
+      <c r="AR7" s="15"/>
+      <c r="AS7" s="15"/>
+      <c r="AT7" s="15"/>
+      <c r="AV7" s="15">
+        <v>6.6</v>
+      </c>
+      <c r="AW7" s="15">
+        <v>3.0819999999999999</v>
+      </c>
+      <c r="AX7" s="15"/>
+      <c r="AY7" s="15"/>
+      <c r="AZ7" s="15"/>
+      <c r="BA7" s="15"/>
+      <c r="BB7" s="15"/>
+      <c r="BC7" s="15"/>
+      <c r="BE7" s="15"/>
+      <c r="BF7" s="15"/>
+      <c r="BG7" s="15"/>
+      <c r="BH7" s="15"/>
+      <c r="BI7" s="15"/>
+      <c r="BJ7" s="15"/>
+      <c r="BK7" s="15"/>
+      <c r="BL7" s="15"/>
+      <c r="BN7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:66" x14ac:dyDescent="0.35">
+      <c r="A8" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="19">
+        <v>11</v>
+      </c>
+      <c r="D8" s="19">
+        <v>14</v>
+      </c>
+      <c r="E8" s="19">
+        <v>85</v>
+      </c>
+      <c r="F8" s="19">
+        <v>140</v>
+      </c>
+      <c r="G8" s="19">
+        <v>7</v>
+      </c>
+      <c r="H8" s="19">
+        <v>28</v>
+      </c>
+      <c r="I8" s="19">
+        <v>19</v>
+      </c>
+      <c r="J8" s="19">
+        <v>17</v>
+      </c>
+      <c r="L8" s="19">
+        <v>0</v>
+      </c>
+      <c r="M8" s="19">
+        <v>0</v>
+      </c>
+      <c r="N8" s="19">
+        <v>0</v>
+      </c>
+      <c r="O8" s="19">
+        <v>0</v>
+      </c>
+      <c r="P8" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="19">
+        <v>0</v>
+      </c>
+      <c r="R8" s="19">
+        <v>0</v>
+      </c>
+      <c r="S8" s="19">
+        <v>0</v>
+      </c>
+      <c r="U8" s="19">
+        <v>4</v>
+      </c>
+      <c r="V8" s="19">
+        <v>0</v>
+      </c>
+      <c r="W8" s="19">
+        <v>0.75</v>
+      </c>
+      <c r="X8" s="19">
+        <v>0.75</v>
+      </c>
+      <c r="Y8" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="19">
+        <v>8.5</v>
+      </c>
+      <c r="AD8" s="19">
+        <v>533</v>
+      </c>
+      <c r="AE8" s="19">
+        <v>219</v>
+      </c>
+      <c r="AF8" s="19">
+        <v>15</v>
+      </c>
+      <c r="AG8" s="19">
+        <v>24</v>
+      </c>
+      <c r="AH8" s="19">
+        <v>15</v>
+      </c>
+      <c r="AI8" s="19">
+        <v>72</v>
+      </c>
+      <c r="AJ8" s="19">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="19">
+        <v>39</v>
+      </c>
+      <c r="AM8" s="19">
+        <v>3</v>
+      </c>
+      <c r="AN8" s="19">
+        <v>3</v>
+      </c>
+      <c r="AO8" s="19">
+        <v>0</v>
+      </c>
+      <c r="AP8" s="19">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="19">
+        <v>0</v>
+      </c>
+      <c r="AR8" s="19">
+        <v>0</v>
+      </c>
+      <c r="AS8" s="19">
+        <v>0</v>
+      </c>
+      <c r="AT8" s="19">
+        <v>2</v>
+      </c>
+      <c r="AV8" s="19">
+        <v>47</v>
+      </c>
+      <c r="AW8" s="19">
+        <v>6</v>
+      </c>
+      <c r="AX8" s="19">
+        <v>0</v>
+      </c>
+      <c r="AY8" s="19">
+        <v>1</v>
+      </c>
+      <c r="AZ8" s="19">
+        <v>0</v>
+      </c>
+      <c r="BA8" s="19">
+        <v>0</v>
+      </c>
+      <c r="BB8" s="19">
+        <v>0</v>
+      </c>
+      <c r="BC8" s="19">
+        <v>40</v>
+      </c>
+      <c r="BE8" s="15">
+        <v>73.3</v>
+      </c>
+      <c r="BF8" s="15"/>
+      <c r="BG8" s="15"/>
+      <c r="BH8" s="15"/>
+      <c r="BI8" s="15"/>
+      <c r="BJ8" s="15"/>
+      <c r="BK8" s="15"/>
+      <c r="BL8" s="15"/>
+    </row>
+    <row r="9" spans="1:66" x14ac:dyDescent="0.35">
+      <c r="A9" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="19">
+        <v>1</v>
+      </c>
+      <c r="D9" s="19">
+        <v>2</v>
+      </c>
+      <c r="E9" s="19">
+        <v>2</v>
+      </c>
+      <c r="F9" s="19">
+        <v>24</v>
+      </c>
+      <c r="G9" s="19">
+        <v>0</v>
+      </c>
+      <c r="H9" s="19">
+        <v>8</v>
+      </c>
+      <c r="I9" s="19">
+        <v>2</v>
+      </c>
+      <c r="J9" s="19">
+        <v>2</v>
+      </c>
+      <c r="L9" s="19">
+        <v>0</v>
+      </c>
+      <c r="M9" s="19">
+        <v>0</v>
+      </c>
+      <c r="N9" s="19">
+        <v>0</v>
+      </c>
+      <c r="O9" s="19">
+        <v>0</v>
+      </c>
+      <c r="P9" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="19">
+        <v>0</v>
+      </c>
+      <c r="R9" s="19">
+        <v>0</v>
+      </c>
+      <c r="S9" s="19">
+        <v>0</v>
+      </c>
+      <c r="U9" s="19">
+        <v>0</v>
+      </c>
+      <c r="V9" s="19">
+        <v>0</v>
+      </c>
+      <c r="W9" s="19">
+        <v>0</v>
+      </c>
+      <c r="X9" s="19">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="19">
+        <v>13</v>
+      </c>
+      <c r="AE9" s="19">
+        <v>14</v>
+      </c>
+      <c r="AF9" s="19">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="19">
+        <v>1</v>
+      </c>
+      <c r="AH9" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="19">
+        <v>4</v>
+      </c>
+      <c r="AJ9" s="19">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="19">
+        <v>2</v>
+      </c>
+      <c r="AM9" s="19">
+        <v>0</v>
+      </c>
+      <c r="AN9" s="19">
+        <v>0</v>
+      </c>
+      <c r="AO9" s="19">
+        <v>0</v>
+      </c>
+      <c r="AP9" s="19">
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="19">
+        <v>0</v>
+      </c>
+      <c r="AR9" s="19">
+        <v>0</v>
+      </c>
+      <c r="AS9" s="19">
+        <v>0</v>
+      </c>
+      <c r="AT9" s="19">
+        <v>0</v>
+      </c>
+      <c r="AV9" s="19">
+        <v>0</v>
+      </c>
+      <c r="AW9" s="19">
+        <v>0</v>
+      </c>
+      <c r="AX9" s="19">
+        <v>0</v>
+      </c>
+      <c r="AY9" s="19">
+        <v>0</v>
+      </c>
+      <c r="AZ9" s="19">
+        <v>0</v>
+      </c>
+      <c r="BA9" s="19">
+        <v>0</v>
+      </c>
+      <c r="BB9" s="19">
+        <v>0</v>
+      </c>
+      <c r="BC9" s="19">
+        <v>0</v>
+      </c>
+      <c r="BE9" s="15"/>
+      <c r="BF9" s="15"/>
+      <c r="BG9" s="15"/>
+      <c r="BH9" s="15"/>
+      <c r="BI9" s="15"/>
+      <c r="BJ9" s="15"/>
+      <c r="BK9" s="15"/>
+      <c r="BL9" s="15"/>
+    </row>
+    <row r="10" spans="1:66" x14ac:dyDescent="0.35">
+      <c r="A10" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="19">
+        <v>2</v>
+      </c>
+      <c r="D10" s="19">
+        <v>6</v>
+      </c>
+      <c r="E10" s="19">
+        <v>1</v>
+      </c>
+      <c r="F10" s="19">
+        <v>47</v>
+      </c>
+      <c r="G10" s="19">
+        <v>2</v>
+      </c>
+      <c r="H10" s="19">
+        <v>4</v>
+      </c>
+      <c r="I10" s="19">
+        <v>4</v>
+      </c>
+      <c r="J10" s="19">
+        <v>2</v>
+      </c>
+      <c r="L10" s="19">
+        <v>0</v>
+      </c>
+      <c r="M10" s="19">
+        <v>0</v>
+      </c>
+      <c r="N10" s="19">
+        <v>0</v>
+      </c>
+      <c r="O10" s="19">
+        <v>0</v>
+      </c>
+      <c r="P10" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="19">
+        <v>0</v>
+      </c>
+      <c r="R10" s="19">
+        <v>0</v>
+      </c>
+      <c r="S10" s="19">
+        <v>0</v>
+      </c>
+      <c r="U10" s="19">
+        <v>1</v>
+      </c>
+      <c r="V10" s="19">
+        <v>1</v>
+      </c>
+      <c r="W10" s="19">
+        <v>0</v>
+      </c>
+      <c r="X10" s="19">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="19">
+        <v>7</v>
+      </c>
+      <c r="AD10" s="19">
+        <v>17</v>
+      </c>
+      <c r="AE10" s="19">
+        <v>50</v>
+      </c>
+      <c r="AF10" s="19">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="19">
+        <v>2</v>
+      </c>
+      <c r="AH10" s="19">
+        <v>2</v>
+      </c>
+      <c r="AI10" s="19">
+        <v>7</v>
+      </c>
+      <c r="AJ10" s="19">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="19">
+        <v>1</v>
+      </c>
+      <c r="AM10" s="19">
+        <v>0</v>
+      </c>
+      <c r="AN10" s="19">
+        <v>0</v>
+      </c>
+      <c r="AO10" s="19">
+        <v>0</v>
+      </c>
+      <c r="AP10" s="19">
+        <v>0</v>
+      </c>
+      <c r="AQ10" s="19">
+        <v>0</v>
+      </c>
+      <c r="AR10" s="19">
+        <v>0</v>
+      </c>
+      <c r="AS10" s="19">
+        <v>0</v>
+      </c>
+      <c r="AT10" s="19">
+        <v>2</v>
+      </c>
+      <c r="AV10" s="19">
+        <v>0</v>
+      </c>
+      <c r="AW10" s="19">
+        <v>0</v>
+      </c>
+      <c r="AX10" s="19">
+        <v>0</v>
+      </c>
+      <c r="AY10" s="19">
+        <v>0</v>
+      </c>
+      <c r="AZ10" s="19">
+        <v>0</v>
+      </c>
+      <c r="BA10" s="19">
+        <v>0</v>
+      </c>
+      <c r="BB10" s="19">
+        <v>0</v>
+      </c>
+      <c r="BC10" s="19">
+        <v>0</v>
+      </c>
+      <c r="BE10" s="15">
+        <v>470.5</v>
+      </c>
+      <c r="BF10" s="15"/>
+      <c r="BG10" s="15"/>
+      <c r="BH10" s="15"/>
+      <c r="BI10" s="15"/>
+      <c r="BJ10" s="15"/>
+      <c r="BK10" s="15"/>
+      <c r="BL10" s="15"/>
+    </row>
+    <row r="11" spans="1:66" x14ac:dyDescent="0.35">
+      <c r="A11" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="19">
+        <v>4</v>
+      </c>
+      <c r="D11" s="19">
+        <v>8</v>
+      </c>
+      <c r="E11" s="19">
+        <v>7</v>
+      </c>
+      <c r="F11" s="19">
+        <v>142</v>
+      </c>
+      <c r="G11" s="19">
+        <v>3</v>
+      </c>
+      <c r="H11" s="19">
+        <v>15</v>
+      </c>
+      <c r="I11" s="19">
+        <v>13</v>
+      </c>
+      <c r="J11" s="19">
+        <v>15</v>
+      </c>
+      <c r="L11" s="19">
+        <v>7</v>
+      </c>
+      <c r="M11" s="19">
+        <v>0</v>
+      </c>
+      <c r="N11" s="19">
+        <v>0</v>
+      </c>
+      <c r="O11" s="19">
+        <v>0</v>
+      </c>
+      <c r="P11" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="19">
+        <v>0</v>
+      </c>
+      <c r="R11" s="19">
+        <v>0</v>
+      </c>
+      <c r="S11" s="19">
+        <v>0</v>
+      </c>
+      <c r="U11" s="19">
+        <v>2</v>
+      </c>
+      <c r="V11" s="19">
+        <v>0</v>
+      </c>
+      <c r="W11" s="19">
+        <v>0</v>
+      </c>
+      <c r="X11" s="19">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="19">
+        <v>2</v>
+      </c>
+      <c r="AD11" s="19">
+        <v>411</v>
+      </c>
+      <c r="AE11" s="19">
+        <v>153</v>
+      </c>
+      <c r="AF11" s="19">
+        <v>2</v>
+      </c>
+      <c r="AG11" s="19">
+        <v>24</v>
+      </c>
+      <c r="AH11" s="19">
+        <v>3</v>
+      </c>
+      <c r="AI11" s="19">
+        <v>27</v>
+      </c>
+      <c r="AJ11" s="19">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="19">
+        <v>16</v>
+      </c>
+      <c r="AM11" s="19">
+        <v>0</v>
+      </c>
+      <c r="AN11" s="19">
+        <v>0</v>
+      </c>
+      <c r="AO11" s="19">
+        <v>0</v>
+      </c>
+      <c r="AP11" s="19">
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="19">
+        <v>0</v>
+      </c>
+      <c r="AR11" s="19">
+        <v>0</v>
+      </c>
+      <c r="AS11" s="19">
+        <v>0</v>
+      </c>
+      <c r="AT11" s="19">
+        <v>2</v>
+      </c>
+      <c r="AV11" s="19">
+        <v>32</v>
+      </c>
+      <c r="AW11" s="19">
+        <v>0</v>
+      </c>
+      <c r="AX11" s="19">
+        <v>0</v>
+      </c>
+      <c r="AY11" s="19">
+        <v>0</v>
+      </c>
+      <c r="AZ11" s="19">
+        <v>0</v>
+      </c>
+      <c r="BA11" s="19">
+        <v>0</v>
+      </c>
+      <c r="BB11" s="19">
+        <v>0</v>
+      </c>
+      <c r="BC11" s="19">
+        <v>0</v>
+      </c>
+      <c r="BE11" s="15">
+        <v>491.33000000000004</v>
+      </c>
+      <c r="BF11" s="15">
+        <v>491.33000000000004</v>
+      </c>
+      <c r="BG11" s="15"/>
+      <c r="BH11" s="15"/>
+      <c r="BI11" s="15"/>
+      <c r="BJ11" s="15"/>
+      <c r="BK11" s="15"/>
+      <c r="BL11" s="15"/>
+      <c r="BN11" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:66" x14ac:dyDescent="0.35">
+      <c r="A12" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="19">
+        <v>0</v>
+      </c>
+      <c r="D12" s="19">
+        <v>0</v>
+      </c>
+      <c r="E12" s="19">
+        <v>7</v>
+      </c>
+      <c r="F12" s="19">
+        <v>142</v>
+      </c>
+      <c r="G12" s="19">
+        <v>5</v>
+      </c>
+      <c r="H12" s="19">
+        <v>3</v>
+      </c>
+      <c r="I12" s="19">
+        <v>3</v>
+      </c>
+      <c r="J12" s="19">
+        <v>1</v>
+      </c>
+      <c r="L12" s="19">
+        <v>0</v>
+      </c>
+      <c r="M12" s="19">
+        <v>2</v>
+      </c>
+      <c r="N12" s="19">
+        <v>0</v>
+      </c>
+      <c r="O12" s="19">
+        <v>0</v>
+      </c>
+      <c r="P12" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="19">
+        <v>0</v>
+      </c>
+      <c r="R12" s="19">
+        <v>0</v>
+      </c>
+      <c r="S12" s="19">
+        <v>0</v>
+      </c>
+      <c r="U12" s="19">
+        <v>0</v>
+      </c>
+      <c r="V12" s="19">
+        <v>1</v>
+      </c>
+      <c r="W12" s="19">
+        <v>0</v>
+      </c>
+      <c r="X12" s="19">
+        <v>2</v>
+      </c>
+      <c r="Y12" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="19">
+        <v>2</v>
+      </c>
+      <c r="AD12" s="19">
+        <v>348</v>
+      </c>
+      <c r="AE12" s="19">
+        <v>623</v>
+      </c>
+      <c r="AF12" s="19">
+        <v>6</v>
+      </c>
+      <c r="AG12" s="19">
+        <v>15</v>
+      </c>
+      <c r="AH12" s="19">
+        <v>56</v>
+      </c>
+      <c r="AI12" s="19">
+        <v>5</v>
+      </c>
+      <c r="AJ12" s="19">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="19">
+        <v>43</v>
+      </c>
+      <c r="AM12" s="19">
+        <v>5</v>
+      </c>
+      <c r="AN12" s="19">
+        <v>22</v>
+      </c>
+      <c r="AO12" s="19">
+        <v>0</v>
+      </c>
+      <c r="AP12" s="19">
+        <v>0</v>
+      </c>
+      <c r="AQ12" s="19">
+        <v>0</v>
+      </c>
+      <c r="AR12" s="19">
+        <v>0</v>
+      </c>
+      <c r="AS12" s="19">
+        <v>0</v>
+      </c>
+      <c r="AT12" s="19">
+        <v>0</v>
+      </c>
+      <c r="AV12" s="19">
+        <v>0</v>
+      </c>
+      <c r="AW12" s="19">
+        <v>0</v>
+      </c>
+      <c r="AX12" s="19">
+        <v>0</v>
+      </c>
+      <c r="AY12" s="19">
+        <v>0</v>
+      </c>
+      <c r="AZ12" s="19">
+        <v>0</v>
+      </c>
+      <c r="BA12" s="19">
+        <v>0</v>
+      </c>
+      <c r="BB12" s="19">
+        <v>0</v>
+      </c>
+      <c r="BC12" s="19">
+        <v>0</v>
+      </c>
+      <c r="BE12" s="15"/>
+      <c r="BF12" s="15"/>
+      <c r="BG12" s="15"/>
+      <c r="BH12" s="15"/>
+      <c r="BI12" s="15"/>
+      <c r="BJ12" s="15"/>
+      <c r="BK12" s="15"/>
+      <c r="BL12" s="15"/>
+    </row>
+    <row r="13" spans="1:66" x14ac:dyDescent="0.35">
+      <c r="A13" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="19">
+        <v>14</v>
+      </c>
+      <c r="D13" s="19">
+        <v>21</v>
+      </c>
+      <c r="E13" s="19">
+        <v>43</v>
+      </c>
+      <c r="F13" s="19">
+        <v>278</v>
+      </c>
+      <c r="G13" s="19">
+        <v>56</v>
+      </c>
+      <c r="H13" s="19">
+        <v>40</v>
+      </c>
+      <c r="I13" s="19">
+        <v>19</v>
+      </c>
+      <c r="J13" s="19">
+        <v>41</v>
+      </c>
+      <c r="L13" s="19">
+        <v>0</v>
+      </c>
+      <c r="M13" s="19">
+        <v>0</v>
+      </c>
+      <c r="N13" s="19">
+        <v>0</v>
+      </c>
+      <c r="O13" s="19">
+        <v>0</v>
+      </c>
+      <c r="P13" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="19">
+        <v>0</v>
+      </c>
+      <c r="R13" s="19">
+        <v>0</v>
+      </c>
+      <c r="S13" s="19">
+        <v>0</v>
+      </c>
+      <c r="U13" s="19">
+        <v>3</v>
+      </c>
+      <c r="V13" s="19">
+        <v>0</v>
+      </c>
+      <c r="W13" s="19">
+        <v>0</v>
+      </c>
+      <c r="X13" s="19">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="19">
+        <v>2</v>
+      </c>
+      <c r="AD13" s="19">
+        <v>1440</v>
+      </c>
+      <c r="AE13" s="19">
+        <v>771</v>
+      </c>
+      <c r="AF13" s="19">
+        <v>11</v>
+      </c>
+      <c r="AG13" s="19">
+        <v>126</v>
+      </c>
+      <c r="AH13" s="19">
+        <v>152</v>
+      </c>
+      <c r="AI13" s="19">
+        <v>60</v>
+      </c>
+      <c r="AJ13" s="19">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="19">
+        <v>25</v>
+      </c>
+      <c r="AM13" s="19">
+        <v>3</v>
+      </c>
+      <c r="AN13" s="19">
+        <v>7</v>
+      </c>
+      <c r="AO13" s="19">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="19">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="19">
+        <v>3</v>
+      </c>
+      <c r="AR13" s="19">
+        <v>0</v>
+      </c>
+      <c r="AS13" s="19">
+        <v>0</v>
+      </c>
+      <c r="AT13" s="19">
+        <v>2</v>
+      </c>
+      <c r="AV13" s="19">
+        <v>17</v>
+      </c>
+      <c r="AW13" s="19">
+        <v>2</v>
+      </c>
+      <c r="AX13" s="19">
+        <v>0</v>
+      </c>
+      <c r="AY13" s="19">
+        <v>0</v>
+      </c>
+      <c r="AZ13" s="19">
+        <v>7</v>
+      </c>
+      <c r="BA13" s="19">
+        <v>0</v>
+      </c>
+      <c r="BB13" s="19">
+        <v>0</v>
+      </c>
+      <c r="BC13" s="19">
+        <v>36</v>
+      </c>
+      <c r="BE13" s="15"/>
+      <c r="BF13" s="15"/>
+      <c r="BG13" s="15"/>
+      <c r="BH13" s="15"/>
+      <c r="BI13" s="15"/>
+      <c r="BJ13" s="15"/>
+      <c r="BK13" s="15"/>
+      <c r="BL13" s="15"/>
+    </row>
+    <row r="14" spans="1:66" x14ac:dyDescent="0.35">
+      <c r="A14" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="19">
+        <v>8</v>
+      </c>
+      <c r="D14" s="19">
+        <v>21</v>
+      </c>
+      <c r="E14" s="19">
+        <v>24</v>
+      </c>
+      <c r="F14" s="19">
+        <v>114</v>
+      </c>
+      <c r="G14" s="19">
+        <v>5</v>
+      </c>
+      <c r="H14" s="19">
+        <v>32</v>
+      </c>
+      <c r="I14" s="19">
+        <v>22</v>
+      </c>
+      <c r="J14" s="19">
+        <v>15</v>
+      </c>
+      <c r="L14" s="19">
+        <v>0</v>
+      </c>
+      <c r="M14" s="19">
+        <v>0</v>
+      </c>
+      <c r="N14" s="19">
+        <v>0</v>
+      </c>
+      <c r="O14" s="19">
+        <v>0</v>
+      </c>
+      <c r="P14" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="19">
+        <v>0</v>
+      </c>
+      <c r="R14" s="19">
+        <v>0</v>
+      </c>
+      <c r="S14" s="19">
+        <v>0</v>
+      </c>
+      <c r="U14" s="19">
+        <v>0</v>
+      </c>
+      <c r="V14" s="19">
+        <v>0</v>
+      </c>
+      <c r="W14" s="19">
+        <v>0</v>
+      </c>
+      <c r="X14" s="19">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="19">
+        <v>43</v>
+      </c>
+      <c r="AE14" s="19">
+        <v>27</v>
+      </c>
+      <c r="AF14" s="19">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="19">
+        <v>7</v>
+      </c>
+      <c r="AH14" s="19">
+        <v>3</v>
+      </c>
+      <c r="AI14" s="19">
+        <v>24</v>
+      </c>
+      <c r="AJ14" s="19">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="19">
+        <v>2</v>
+      </c>
+      <c r="AM14" s="19">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="19">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="19">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="19">
+        <v>2</v>
+      </c>
+      <c r="AQ14" s="19">
+        <v>0</v>
+      </c>
+      <c r="AR14" s="19">
+        <v>0</v>
+      </c>
+      <c r="AS14" s="19">
+        <v>0</v>
+      </c>
+      <c r="AT14" s="19">
+        <v>2</v>
+      </c>
+      <c r="AV14" s="19">
+        <v>0</v>
+      </c>
+      <c r="AW14" s="19">
+        <v>0</v>
+      </c>
+      <c r="AX14" s="19">
+        <v>0</v>
+      </c>
+      <c r="AY14" s="19">
+        <v>0</v>
+      </c>
+      <c r="AZ14" s="19">
+        <v>0</v>
+      </c>
+      <c r="BA14" s="19">
+        <v>0</v>
+      </c>
+      <c r="BB14" s="19">
+        <v>0</v>
+      </c>
+      <c r="BC14" s="19">
+        <v>0</v>
+      </c>
+      <c r="BE14" s="15"/>
+      <c r="BF14" s="15"/>
+      <c r="BG14" s="15"/>
+      <c r="BH14" s="15"/>
+      <c r="BI14" s="15"/>
+      <c r="BJ14" s="15"/>
+      <c r="BK14" s="15"/>
+      <c r="BL14" s="15"/>
+    </row>
+    <row r="15" spans="1:66" x14ac:dyDescent="0.35">
+      <c r="A15" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="19">
+        <v>0</v>
+      </c>
+      <c r="D15" s="19">
+        <v>19</v>
+      </c>
+      <c r="E15" s="19">
+        <v>5</v>
+      </c>
+      <c r="F15" s="19">
+        <v>15</v>
+      </c>
+      <c r="G15" s="19">
+        <v>2</v>
+      </c>
+      <c r="H15" s="19">
+        <v>4</v>
+      </c>
+      <c r="I15" s="19">
+        <v>2</v>
+      </c>
+      <c r="J15" s="19">
+        <v>0</v>
+      </c>
+      <c r="L15" s="19">
+        <v>0</v>
+      </c>
+      <c r="M15" s="19">
+        <v>0</v>
+      </c>
+      <c r="N15" s="19">
+        <v>0</v>
+      </c>
+      <c r="O15" s="19">
+        <v>0</v>
+      </c>
+      <c r="P15" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="19">
+        <v>0</v>
+      </c>
+      <c r="R15" s="19">
+        <v>0</v>
+      </c>
+      <c r="S15" s="19">
+        <v>0</v>
+      </c>
+      <c r="U15" s="19">
+        <v>0</v>
+      </c>
+      <c r="V15" s="19">
+        <v>0</v>
+      </c>
+      <c r="W15" s="19">
+        <v>0</v>
+      </c>
+      <c r="X15" s="19">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="19">
+        <v>3</v>
+      </c>
+      <c r="AE15" s="19">
+        <v>117</v>
+      </c>
+      <c r="AF15" s="19">
+        <v>2</v>
+      </c>
+      <c r="AG15" s="19">
+        <v>6</v>
+      </c>
+      <c r="AH15" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="19">
+        <v>9</v>
+      </c>
+      <c r="AJ15" s="19">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="19">
+        <v>1</v>
+      </c>
+      <c r="AM15" s="19">
+        <v>0</v>
+      </c>
+      <c r="AN15" s="19">
+        <v>0</v>
+      </c>
+      <c r="AO15" s="19">
+        <v>0</v>
+      </c>
+      <c r="AP15" s="19">
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="19">
+        <v>0</v>
+      </c>
+      <c r="AR15" s="19">
+        <v>0</v>
+      </c>
+      <c r="AS15" s="19">
+        <v>0</v>
+      </c>
+      <c r="AT15" s="19">
+        <v>0</v>
+      </c>
+      <c r="AV15" s="19">
+        <v>0</v>
+      </c>
+      <c r="AW15" s="19">
+        <v>0</v>
+      </c>
+      <c r="AX15" s="19">
+        <v>0</v>
+      </c>
+      <c r="AY15" s="19">
+        <v>0</v>
+      </c>
+      <c r="AZ15" s="19">
+        <v>0</v>
+      </c>
+      <c r="BA15" s="19">
+        <v>0</v>
+      </c>
+      <c r="BB15" s="19">
+        <v>0</v>
+      </c>
+      <c r="BC15" s="19">
+        <v>0</v>
+      </c>
+      <c r="BE15" s="15"/>
+      <c r="BF15" s="15"/>
+      <c r="BG15" s="15"/>
+      <c r="BH15" s="15"/>
+      <c r="BI15" s="15"/>
+      <c r="BJ15" s="15"/>
+      <c r="BK15" s="15"/>
+      <c r="BL15" s="15"/>
+    </row>
+    <row r="16" spans="1:66" x14ac:dyDescent="0.35">
+      <c r="A16" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="19">
+        <v>0</v>
+      </c>
+      <c r="D16" s="19">
+        <v>7</v>
+      </c>
+      <c r="E16" s="19">
+        <v>2</v>
+      </c>
+      <c r="F16" s="19">
+        <v>44</v>
+      </c>
+      <c r="G16" s="19">
+        <v>3</v>
+      </c>
+      <c r="H16" s="19">
+        <v>1</v>
+      </c>
+      <c r="I16" s="19">
+        <v>1</v>
+      </c>
+      <c r="J16" s="19">
+        <v>0</v>
+      </c>
+      <c r="L16" s="19">
+        <v>0</v>
+      </c>
+      <c r="M16" s="19">
+        <v>0</v>
+      </c>
+      <c r="N16" s="19">
+        <v>0</v>
+      </c>
+      <c r="O16" s="19">
+        <v>0</v>
+      </c>
+      <c r="P16" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="19">
+        <v>0</v>
+      </c>
+      <c r="R16" s="19">
+        <v>0</v>
+      </c>
+      <c r="S16" s="19">
+        <v>0</v>
+      </c>
+      <c r="U16" s="19">
+        <v>0</v>
+      </c>
+      <c r="V16" s="19">
+        <v>1</v>
+      </c>
+      <c r="W16" s="19">
+        <v>0</v>
+      </c>
+      <c r="X16" s="19">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="19">
+        <v>3</v>
+      </c>
+      <c r="AD16" s="19">
+        <v>3</v>
+      </c>
+      <c r="AE16" s="19">
+        <v>192</v>
+      </c>
+      <c r="AF16" s="19">
+        <v>1</v>
+      </c>
+      <c r="AG16" s="19">
+        <v>9</v>
+      </c>
+      <c r="AH16" s="19">
+        <v>1</v>
+      </c>
+      <c r="AI16" s="19">
+        <v>4</v>
+      </c>
+      <c r="AJ16" s="19">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="19">
+        <v>4</v>
+      </c>
+      <c r="AM16" s="19">
+        <v>0</v>
+      </c>
+      <c r="AN16" s="19">
+        <v>0</v>
+      </c>
+      <c r="AO16" s="19">
+        <v>0</v>
+      </c>
+      <c r="AP16" s="19">
+        <v>0</v>
+      </c>
+      <c r="AQ16" s="19">
+        <v>0</v>
+      </c>
+      <c r="AR16" s="19">
+        <v>0</v>
+      </c>
+      <c r="AS16" s="19">
+        <v>0</v>
+      </c>
+      <c r="AT16" s="19">
+        <v>0</v>
+      </c>
+      <c r="AV16" s="19">
+        <v>0</v>
+      </c>
+      <c r="AW16" s="19">
+        <v>176</v>
+      </c>
+      <c r="AX16" s="19">
+        <v>0</v>
+      </c>
+      <c r="AY16" s="19">
+        <v>2</v>
+      </c>
+      <c r="AZ16" s="19">
+        <v>0</v>
+      </c>
+      <c r="BA16" s="19">
+        <v>0</v>
+      </c>
+      <c r="BB16" s="19">
+        <v>0</v>
+      </c>
+      <c r="BC16" s="19">
+        <v>0</v>
+      </c>
+      <c r="BE16" s="15"/>
+      <c r="BF16" s="15">
+        <v>43.451999999999998</v>
+      </c>
+      <c r="BG16" s="15"/>
+      <c r="BH16" s="15"/>
+      <c r="BI16" s="15"/>
+      <c r="BJ16" s="15"/>
+      <c r="BK16" s="15"/>
+      <c r="BL16" s="15"/>
+    </row>
+    <row r="17" spans="1:66" x14ac:dyDescent="0.35">
+      <c r="A17" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="19">
+        <v>1</v>
+      </c>
+      <c r="D17" s="19">
+        <v>63</v>
+      </c>
+      <c r="E17" s="19">
+        <v>4</v>
+      </c>
+      <c r="F17" s="19">
+        <v>97.619718309859095</v>
+      </c>
+      <c r="G17" s="19">
+        <v>32.380281690140798</v>
+      </c>
+      <c r="H17" s="19">
+        <v>10</v>
+      </c>
+      <c r="I17" s="19">
+        <v>8</v>
+      </c>
+      <c r="J17" s="19">
+        <v>4</v>
+      </c>
+      <c r="L17" s="19">
+        <v>0</v>
+      </c>
+      <c r="M17" s="19">
+        <v>0</v>
+      </c>
+      <c r="N17" s="19">
+        <v>0</v>
+      </c>
+      <c r="O17" s="19">
+        <v>0</v>
+      </c>
+      <c r="P17" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="19">
+        <v>0</v>
+      </c>
+      <c r="R17" s="19">
+        <v>0</v>
+      </c>
+      <c r="S17" s="19">
+        <v>2</v>
+      </c>
+      <c r="U17" s="19">
+        <v>0</v>
+      </c>
+      <c r="V17" s="19">
+        <v>0</v>
+      </c>
+      <c r="W17" s="19">
+        <v>0</v>
+      </c>
+      <c r="X17" s="19">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="19">
+        <v>5</v>
+      </c>
+      <c r="AD17" s="19">
+        <v>52</v>
+      </c>
+      <c r="AE17" s="19">
+        <v>324</v>
+      </c>
+      <c r="AF17" s="19">
+        <v>3</v>
+      </c>
+      <c r="AG17" s="19">
+        <v>6</v>
+      </c>
+      <c r="AH17" s="19">
+        <v>27</v>
+      </c>
+      <c r="AI17" s="19">
+        <v>26</v>
+      </c>
+      <c r="AJ17" s="19">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="19">
+        <v>4</v>
+      </c>
+      <c r="AM17" s="19">
+        <v>0</v>
+      </c>
+      <c r="AN17" s="19">
+        <v>0</v>
+      </c>
+      <c r="AO17" s="19">
+        <v>0</v>
+      </c>
+      <c r="AP17" s="19">
+        <v>0</v>
+      </c>
+      <c r="AQ17" s="19">
+        <v>0</v>
+      </c>
+      <c r="AR17" s="19">
+        <v>0</v>
+      </c>
+      <c r="AS17" s="19">
+        <v>0</v>
+      </c>
+      <c r="AT17" s="19">
+        <v>0</v>
+      </c>
+      <c r="AV17" s="19">
+        <v>2</v>
+      </c>
+      <c r="AW17" s="19">
+        <v>5</v>
+      </c>
+      <c r="AX17" s="19">
+        <v>0</v>
+      </c>
+      <c r="AY17" s="19">
+        <v>0</v>
+      </c>
+      <c r="AZ17" s="19">
+        <v>9</v>
+      </c>
+      <c r="BA17" s="19">
+        <v>0</v>
+      </c>
+      <c r="BB17" s="19">
+        <v>0</v>
+      </c>
+      <c r="BC17" s="19">
+        <v>1</v>
+      </c>
+      <c r="BE17" s="15"/>
+      <c r="BF17" s="15"/>
+      <c r="BG17" s="15"/>
+      <c r="BH17" s="15"/>
+      <c r="BI17" s="15"/>
+      <c r="BJ17" s="15"/>
+      <c r="BK17" s="15"/>
+      <c r="BL17" s="15"/>
+    </row>
+    <row r="18" spans="1:66" x14ac:dyDescent="0.35">
+      <c r="A18" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="19">
+        <v>0</v>
+      </c>
+      <c r="D18" s="19">
+        <v>25</v>
+      </c>
+      <c r="E18" s="19">
+        <v>4</v>
+      </c>
+      <c r="F18" s="19">
+        <v>50.473684210526301</v>
+      </c>
+      <c r="G18" s="19">
+        <v>54.5263157894736</v>
+      </c>
+      <c r="H18" s="19">
+        <v>6</v>
+      </c>
+      <c r="I18" s="19">
+        <v>5</v>
+      </c>
+      <c r="J18" s="19">
+        <v>2</v>
+      </c>
+      <c r="L18" s="19">
+        <v>0</v>
+      </c>
+      <c r="M18" s="19">
+        <v>0</v>
+      </c>
+      <c r="N18" s="19">
+        <v>0</v>
+      </c>
+      <c r="O18" s="19">
+        <v>0</v>
+      </c>
+      <c r="P18" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="19">
+        <v>0</v>
+      </c>
+      <c r="R18" s="19">
+        <v>0</v>
+      </c>
+      <c r="S18" s="19">
+        <v>0</v>
+      </c>
+      <c r="U18" s="19">
+        <v>0</v>
+      </c>
+      <c r="V18" s="19">
+        <v>0</v>
+      </c>
+      <c r="W18" s="19">
+        <v>0</v>
+      </c>
+      <c r="X18" s="19">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="19">
+        <v>1</v>
+      </c>
+      <c r="AD18" s="19">
+        <v>33</v>
+      </c>
+      <c r="AE18" s="19">
+        <v>200</v>
+      </c>
+      <c r="AF18" s="19">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="19">
+        <v>15</v>
+      </c>
+      <c r="AH18" s="19">
+        <v>6</v>
+      </c>
+      <c r="AI18" s="19">
+        <v>19</v>
+      </c>
+      <c r="AJ18" s="19">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="19">
+        <v>3</v>
+      </c>
+      <c r="AM18" s="19">
+        <v>1</v>
+      </c>
+      <c r="AN18" s="19">
+        <v>1</v>
+      </c>
+      <c r="AO18" s="19">
+        <v>0</v>
+      </c>
+      <c r="AP18" s="19">
+        <v>0</v>
+      </c>
+      <c r="AQ18" s="19">
+        <v>0</v>
+      </c>
+      <c r="AR18" s="19">
+        <v>0</v>
+      </c>
+      <c r="AS18" s="19">
+        <v>0</v>
+      </c>
+      <c r="AT18" s="19">
+        <v>1</v>
+      </c>
+      <c r="AV18" s="19">
+        <v>0</v>
+      </c>
+      <c r="AW18" s="19">
+        <v>0</v>
+      </c>
+      <c r="AX18" s="19">
+        <v>0</v>
+      </c>
+      <c r="AY18" s="19">
+        <v>0</v>
+      </c>
+      <c r="AZ18" s="19">
+        <v>0</v>
+      </c>
+      <c r="BA18" s="19">
+        <v>0</v>
+      </c>
+      <c r="BB18" s="19">
+        <v>0</v>
+      </c>
+      <c r="BC18" s="19">
+        <v>0</v>
+      </c>
+      <c r="BE18" s="15"/>
+      <c r="BF18" s="15"/>
+      <c r="BG18" s="15"/>
+      <c r="BH18" s="15"/>
+      <c r="BI18" s="15"/>
+      <c r="BJ18" s="15"/>
+      <c r="BK18" s="15"/>
+      <c r="BL18" s="15"/>
+    </row>
+    <row r="19" spans="1:66" x14ac:dyDescent="0.35">
+      <c r="A19" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="19">
+        <v>1</v>
+      </c>
+      <c r="D19" s="19">
+        <v>22</v>
+      </c>
+      <c r="E19" s="19">
+        <v>3</v>
+      </c>
+      <c r="F19" s="19">
+        <v>66</v>
+      </c>
+      <c r="G19" s="19">
+        <v>9</v>
+      </c>
+      <c r="H19" s="19">
+        <v>20</v>
+      </c>
+      <c r="I19" s="19">
+        <v>12</v>
+      </c>
+      <c r="J19" s="19">
+        <v>10</v>
+      </c>
+      <c r="L19" s="19">
+        <v>0</v>
+      </c>
+      <c r="M19" s="19">
+        <v>0</v>
+      </c>
+      <c r="N19" s="19">
+        <v>0</v>
+      </c>
+      <c r="O19" s="19">
+        <v>0</v>
+      </c>
+      <c r="P19" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="19">
+        <v>0</v>
+      </c>
+      <c r="R19" s="19">
+        <v>0</v>
+      </c>
+      <c r="S19" s="19">
+        <v>0</v>
+      </c>
+      <c r="U19" s="19">
+        <v>0</v>
+      </c>
+      <c r="V19" s="19">
+        <v>0</v>
+      </c>
+      <c r="W19" s="19">
+        <v>0</v>
+      </c>
+      <c r="X19" s="19">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="19">
+        <v>2</v>
+      </c>
+      <c r="AD19" s="19">
+        <v>51</v>
+      </c>
+      <c r="AE19" s="19">
+        <v>175</v>
+      </c>
+      <c r="AF19" s="19">
+        <v>0</v>
+      </c>
+      <c r="AG19" s="19">
+        <v>3</v>
+      </c>
+      <c r="AH19" s="19">
+        <v>2</v>
+      </c>
+      <c r="AI19" s="19">
+        <v>40</v>
+      </c>
+      <c r="AJ19" s="19">
+        <v>0</v>
+      </c>
+      <c r="AK19" s="19">
+        <v>4</v>
+      </c>
+      <c r="AM19" s="19">
+        <v>0</v>
+      </c>
+      <c r="AN19" s="19">
+        <v>0</v>
+      </c>
+      <c r="AO19" s="19">
+        <v>0</v>
+      </c>
+      <c r="AP19" s="19">
+        <v>1</v>
+      </c>
+      <c r="AQ19" s="19">
+        <v>0</v>
+      </c>
+      <c r="AR19" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS19" s="19">
+        <v>0</v>
+      </c>
+      <c r="AT19" s="19">
+        <v>2</v>
+      </c>
+      <c r="AV19" s="19">
+        <v>0</v>
+      </c>
+      <c r="AW19" s="19">
+        <v>0</v>
+      </c>
+      <c r="AX19" s="19">
+        <v>0</v>
+      </c>
+      <c r="AY19" s="19">
+        <v>0</v>
+      </c>
+      <c r="AZ19" s="19">
+        <v>0</v>
+      </c>
+      <c r="BA19" s="19">
+        <v>0</v>
+      </c>
+      <c r="BB19" s="19">
+        <v>0</v>
+      </c>
+      <c r="BC19" s="19">
+        <v>0</v>
+      </c>
+      <c r="BE19" s="15"/>
+      <c r="BF19" s="15"/>
+      <c r="BG19" s="15"/>
+      <c r="BH19" s="15"/>
+      <c r="BI19" s="15"/>
+      <c r="BJ19" s="15"/>
+      <c r="BK19" s="15"/>
+      <c r="BL19" s="15"/>
+    </row>
+    <row r="20" spans="1:66" x14ac:dyDescent="0.35">
+      <c r="A20" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="19">
+        <v>1</v>
+      </c>
+      <c r="D20" s="19">
+        <v>5</v>
+      </c>
+      <c r="E20" s="19">
+        <v>12</v>
+      </c>
+      <c r="F20" s="19">
+        <v>20</v>
+      </c>
+      <c r="G20" s="19">
+        <v>21</v>
+      </c>
+      <c r="H20" s="19">
+        <v>21</v>
+      </c>
+      <c r="I20" s="19">
+        <v>7</v>
+      </c>
+      <c r="J20" s="19">
+        <v>7</v>
+      </c>
+      <c r="L20" s="19">
+        <v>0</v>
+      </c>
+      <c r="M20" s="19">
+        <v>0</v>
+      </c>
+      <c r="N20" s="19">
+        <v>0</v>
+      </c>
+      <c r="O20" s="19">
+        <v>0</v>
+      </c>
+      <c r="P20" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="19">
+        <v>0</v>
+      </c>
+      <c r="R20" s="19">
+        <v>0</v>
+      </c>
+      <c r="S20" s="19">
+        <v>0</v>
+      </c>
+      <c r="U20" s="19">
+        <v>0</v>
+      </c>
+      <c r="V20" s="19">
+        <v>0</v>
+      </c>
+      <c r="W20" s="19">
+        <v>0</v>
+      </c>
+      <c r="X20" s="19">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="19">
+        <v>8</v>
+      </c>
+      <c r="AE20" s="19">
+        <v>5</v>
+      </c>
+      <c r="AF20" s="19">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="19">
+        <v>2</v>
+      </c>
+      <c r="AH20" s="19">
+        <v>1</v>
+      </c>
+      <c r="AI20" s="19">
+        <v>13</v>
+      </c>
+      <c r="AJ20" s="19">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="19">
+        <v>3</v>
+      </c>
+      <c r="AM20" s="19">
+        <v>0</v>
+      </c>
+      <c r="AN20" s="19">
+        <v>0</v>
+      </c>
+      <c r="AO20" s="19">
+        <v>0</v>
+      </c>
+      <c r="AP20" s="19">
+        <v>0</v>
+      </c>
+      <c r="AQ20" s="19">
+        <v>0</v>
+      </c>
+      <c r="AR20" s="19">
+        <v>0</v>
+      </c>
+      <c r="AS20" s="19">
+        <v>0</v>
+      </c>
+      <c r="AT20" s="19">
+        <v>0</v>
+      </c>
+      <c r="AV20" s="19">
+        <v>0</v>
+      </c>
+      <c r="AW20" s="19">
+        <v>0</v>
+      </c>
+      <c r="AX20" s="19">
+        <v>0</v>
+      </c>
+      <c r="AY20" s="19">
+        <v>0</v>
+      </c>
+      <c r="AZ20" s="19">
+        <v>0</v>
+      </c>
+      <c r="BA20" s="19">
+        <v>0</v>
+      </c>
+      <c r="BB20" s="19">
+        <v>0</v>
+      </c>
+      <c r="BC20" s="19">
+        <v>0</v>
+      </c>
+      <c r="BE20" s="15"/>
+      <c r="BF20" s="15"/>
+      <c r="BG20" s="15"/>
+      <c r="BH20" s="15"/>
+      <c r="BI20" s="15"/>
+      <c r="BJ20" s="15"/>
+      <c r="BK20" s="15"/>
+      <c r="BL20" s="15"/>
+    </row>
+    <row r="21" spans="1:66" x14ac:dyDescent="0.35">
+      <c r="A21" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="19">
+        <v>0</v>
+      </c>
+      <c r="D21" s="19">
+        <v>5</v>
+      </c>
+      <c r="E21" s="19">
+        <v>1</v>
+      </c>
+      <c r="F21" s="19">
+        <v>15</v>
+      </c>
+      <c r="G21" s="19">
+        <v>4</v>
+      </c>
+      <c r="H21" s="19">
+        <v>7</v>
+      </c>
+      <c r="I21" s="19">
+        <v>3</v>
+      </c>
+      <c r="J21" s="19">
+        <v>4</v>
+      </c>
+      <c r="L21" s="19">
+        <v>0</v>
+      </c>
+      <c r="M21" s="19">
+        <v>0</v>
+      </c>
+      <c r="N21" s="19">
+        <v>0</v>
+      </c>
+      <c r="O21" s="19">
+        <v>0</v>
+      </c>
+      <c r="P21" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="19">
+        <v>0</v>
+      </c>
+      <c r="R21" s="19">
+        <v>0</v>
+      </c>
+      <c r="S21" s="19">
+        <v>0</v>
+      </c>
+      <c r="U21" s="19">
+        <v>0</v>
+      </c>
+      <c r="V21" s="19">
+        <v>0</v>
+      </c>
+      <c r="W21" s="19">
+        <v>0</v>
+      </c>
+      <c r="X21" s="19">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="19">
+        <v>5</v>
+      </c>
+      <c r="AE21" s="19">
+        <v>16</v>
+      </c>
+      <c r="AF21" s="19">
+        <v>0</v>
+      </c>
+      <c r="AG21" s="19">
+        <v>2</v>
+      </c>
+      <c r="AH21" s="19">
+        <v>1</v>
+      </c>
+      <c r="AI21" s="19">
+        <v>10</v>
+      </c>
+      <c r="AJ21" s="19">
+        <v>0</v>
+      </c>
+      <c r="AK21" s="19">
+        <v>3</v>
+      </c>
+      <c r="AM21" s="19">
+        <v>0</v>
+      </c>
+      <c r="AN21" s="19">
+        <v>0</v>
+      </c>
+      <c r="AO21" s="19">
+        <v>0</v>
+      </c>
+      <c r="AP21" s="19">
+        <v>0</v>
+      </c>
+      <c r="AQ21" s="19">
+        <v>0</v>
+      </c>
+      <c r="AR21" s="19">
+        <v>0</v>
+      </c>
+      <c r="AS21" s="19">
+        <v>0</v>
+      </c>
+      <c r="AT21" s="19">
+        <v>0</v>
+      </c>
+      <c r="AV21" s="19">
+        <v>0</v>
+      </c>
+      <c r="AW21" s="19">
+        <v>0</v>
+      </c>
+      <c r="AX21" s="19">
+        <v>0</v>
+      </c>
+      <c r="AY21" s="19">
+        <v>0</v>
+      </c>
+      <c r="AZ21" s="19">
+        <v>0</v>
+      </c>
+      <c r="BA21" s="19">
+        <v>0</v>
+      </c>
+      <c r="BB21" s="19">
+        <v>0</v>
+      </c>
+      <c r="BC21" s="19">
+        <v>0</v>
+      </c>
+      <c r="BE21" s="15"/>
+      <c r="BF21" s="15"/>
+      <c r="BG21" s="15"/>
+      <c r="BH21" s="15"/>
+      <c r="BI21" s="15"/>
+      <c r="BJ21" s="15"/>
+      <c r="BK21" s="15"/>
+      <c r="BL21" s="15"/>
+    </row>
+    <row r="22" spans="1:66" x14ac:dyDescent="0.35">
+      <c r="A22" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="19">
+        <v>0</v>
+      </c>
+      <c r="D22" s="19">
+        <v>4</v>
+      </c>
+      <c r="E22" s="19">
+        <v>3</v>
+      </c>
+      <c r="F22" s="19">
+        <v>31</v>
+      </c>
+      <c r="G22" s="19">
+        <v>3</v>
+      </c>
+      <c r="H22" s="19">
+        <v>15</v>
+      </c>
+      <c r="I22" s="19">
+        <v>7</v>
+      </c>
+      <c r="J22" s="19">
+        <v>12</v>
+      </c>
+      <c r="L22" s="19">
+        <v>0</v>
+      </c>
+      <c r="M22" s="19">
+        <v>0</v>
+      </c>
+      <c r="N22" s="19">
+        <v>0</v>
+      </c>
+      <c r="O22" s="19">
+        <v>0</v>
+      </c>
+      <c r="P22" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="19">
+        <v>0</v>
+      </c>
+      <c r="R22" s="19">
+        <v>0</v>
+      </c>
+      <c r="S22" s="19">
+        <v>0</v>
+      </c>
+      <c r="U22" s="19">
+        <v>0</v>
+      </c>
+      <c r="V22" s="19">
+        <v>0</v>
+      </c>
+      <c r="W22" s="19">
+        <v>0</v>
+      </c>
+      <c r="X22" s="19">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="19">
+        <v>3</v>
+      </c>
+      <c r="Z22" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="19">
+        <v>5</v>
+      </c>
+      <c r="AE22" s="19">
+        <v>20</v>
+      </c>
+      <c r="AF22" s="19">
+        <v>1</v>
+      </c>
+      <c r="AG22" s="19">
+        <v>3</v>
+      </c>
+      <c r="AH22" s="19">
+        <v>1</v>
+      </c>
+      <c r="AI22" s="19">
+        <v>25</v>
+      </c>
+      <c r="AJ22" s="19">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="19">
+        <v>5</v>
+      </c>
+      <c r="AM22" s="19">
+        <v>0</v>
+      </c>
+      <c r="AN22" s="19">
+        <v>2</v>
+      </c>
+      <c r="AO22" s="19">
+        <v>0</v>
+      </c>
+      <c r="AP22" s="19">
+        <v>0</v>
+      </c>
+      <c r="AQ22" s="19">
+        <v>0</v>
+      </c>
+      <c r="AR22" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS22" s="19">
+        <v>0</v>
+      </c>
+      <c r="AT22" s="19">
+        <v>1</v>
+      </c>
+      <c r="AV22" s="19">
+        <v>0</v>
+      </c>
+      <c r="AW22" s="19">
+        <v>0</v>
+      </c>
+      <c r="AX22" s="19">
+        <v>0</v>
+      </c>
+      <c r="AY22" s="19">
+        <v>0</v>
+      </c>
+      <c r="AZ22" s="19">
+        <v>0</v>
+      </c>
+      <c r="BA22" s="19">
+        <v>0</v>
+      </c>
+      <c r="BB22" s="19">
+        <v>0</v>
+      </c>
+      <c r="BC22" s="19">
+        <v>0</v>
+      </c>
+      <c r="BE22" s="15"/>
+      <c r="BF22" s="15"/>
+      <c r="BG22" s="15"/>
+      <c r="BH22" s="15"/>
+      <c r="BI22" s="15"/>
+      <c r="BJ22" s="15"/>
+      <c r="BK22" s="15"/>
+      <c r="BL22" s="15"/>
+    </row>
+    <row r="23" spans="1:66" x14ac:dyDescent="0.35">
+      <c r="A23" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="19">
+        <v>1</v>
+      </c>
+      <c r="D23" s="19">
+        <v>1</v>
+      </c>
+      <c r="E23" s="19">
+        <v>2</v>
+      </c>
+      <c r="F23" s="19">
+        <v>13</v>
+      </c>
+      <c r="G23" s="19">
+        <v>1</v>
+      </c>
+      <c r="H23" s="19">
+        <v>6</v>
+      </c>
+      <c r="I23" s="19">
+        <v>2</v>
+      </c>
+      <c r="J23" s="19">
+        <v>1</v>
+      </c>
+      <c r="L23" s="19">
+        <v>0</v>
+      </c>
+      <c r="M23" s="19">
+        <v>0</v>
+      </c>
+      <c r="N23" s="19">
+        <v>0</v>
+      </c>
+      <c r="O23" s="19">
+        <v>0</v>
+      </c>
+      <c r="P23" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="19">
+        <v>0</v>
+      </c>
+      <c r="R23" s="19">
+        <v>0</v>
+      </c>
+      <c r="S23" s="19">
+        <v>0</v>
+      </c>
+      <c r="U23" s="19">
+        <v>0</v>
+      </c>
+      <c r="V23" s="19">
+        <v>0</v>
+      </c>
+      <c r="W23" s="19">
+        <v>0</v>
+      </c>
+      <c r="X23" s="19">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="19">
+        <v>4</v>
+      </c>
+      <c r="AE23" s="19">
+        <v>24</v>
+      </c>
+      <c r="AF23" s="19">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="19">
+        <v>0</v>
+      </c>
+      <c r="AH23" s="19">
+        <v>1</v>
+      </c>
+      <c r="AI23" s="19">
+        <v>10</v>
+      </c>
+      <c r="AJ23" s="19">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="19">
+        <v>1</v>
+      </c>
+      <c r="AM23" s="19">
+        <v>0</v>
+      </c>
+      <c r="AN23" s="19">
+        <v>0</v>
+      </c>
+      <c r="AO23" s="19">
+        <v>0</v>
+      </c>
+      <c r="AP23" s="19">
+        <v>0</v>
+      </c>
+      <c r="AQ23" s="19">
+        <v>0</v>
+      </c>
+      <c r="AR23" s="19">
+        <v>0</v>
+      </c>
+      <c r="AS23" s="19">
+        <v>0</v>
+      </c>
+      <c r="AT23" s="19">
+        <v>0</v>
+      </c>
+      <c r="AV23" s="19">
+        <v>0</v>
+      </c>
+      <c r="AW23" s="19">
+        <v>0</v>
+      </c>
+      <c r="AX23" s="19">
+        <v>0</v>
+      </c>
+      <c r="AY23" s="19">
+        <v>0</v>
+      </c>
+      <c r="AZ23" s="19">
+        <v>0</v>
+      </c>
+      <c r="BA23" s="19">
+        <v>0</v>
+      </c>
+      <c r="BB23" s="19">
+        <v>0</v>
+      </c>
+      <c r="BC23" s="19">
+        <v>0</v>
+      </c>
+      <c r="BE23" s="15"/>
+      <c r="BF23" s="15"/>
+      <c r="BG23" s="15"/>
+      <c r="BH23" s="15"/>
+      <c r="BI23" s="15"/>
+      <c r="BJ23" s="15"/>
+      <c r="BK23" s="15"/>
+      <c r="BL23" s="15"/>
+    </row>
+    <row r="24" spans="1:66" x14ac:dyDescent="0.35">
+      <c r="A24" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="19">
+        <v>0</v>
+      </c>
+      <c r="D24" s="19">
+        <v>4</v>
+      </c>
+      <c r="E24" s="19">
+        <v>3</v>
+      </c>
+      <c r="F24" s="19">
+        <v>9</v>
+      </c>
+      <c r="G24" s="19">
+        <v>1</v>
+      </c>
+      <c r="H24" s="19">
+        <v>8</v>
+      </c>
+      <c r="I24" s="19">
+        <v>5</v>
+      </c>
+      <c r="J24" s="19">
+        <v>1</v>
+      </c>
+      <c r="L24" s="19">
+        <v>0</v>
+      </c>
+      <c r="M24" s="19">
+        <v>0</v>
+      </c>
+      <c r="N24" s="19">
+        <v>0</v>
+      </c>
+      <c r="O24" s="19">
+        <v>0</v>
+      </c>
+      <c r="P24" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="19">
+        <v>0</v>
+      </c>
+      <c r="R24" s="19">
+        <v>0</v>
+      </c>
+      <c r="S24" s="19">
+        <v>0</v>
+      </c>
+      <c r="U24" s="19">
+        <v>0</v>
+      </c>
+      <c r="V24" s="19">
+        <v>0</v>
+      </c>
+      <c r="W24" s="19">
+        <v>0</v>
+      </c>
+      <c r="X24" s="19">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="19">
+        <v>9</v>
+      </c>
+      <c r="AE24" s="19">
+        <v>6</v>
+      </c>
+      <c r="AF24" s="19">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="19">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="19">
+        <v>1</v>
+      </c>
+      <c r="AI24" s="19">
+        <v>9</v>
+      </c>
+      <c r="AJ24" s="19">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="19">
+        <v>2</v>
+      </c>
+      <c r="AM24" s="19">
+        <v>0</v>
+      </c>
+      <c r="AN24" s="19">
+        <v>0</v>
+      </c>
+      <c r="AO24" s="19">
+        <v>0</v>
+      </c>
+      <c r="AP24" s="19">
+        <v>0</v>
+      </c>
+      <c r="AQ24" s="19">
+        <v>0</v>
+      </c>
+      <c r="AR24" s="19">
+        <v>0</v>
+      </c>
+      <c r="AS24" s="19">
+        <v>0</v>
+      </c>
+      <c r="AT24" s="19">
+        <v>0</v>
+      </c>
+      <c r="AV24" s="19">
+        <v>0</v>
+      </c>
+      <c r="AW24" s="19">
+        <v>0</v>
+      </c>
+      <c r="AX24" s="19">
+        <v>0</v>
+      </c>
+      <c r="AY24" s="19">
+        <v>0</v>
+      </c>
+      <c r="AZ24" s="19">
+        <v>0</v>
+      </c>
+      <c r="BA24" s="19">
+        <v>0</v>
+      </c>
+      <c r="BB24" s="19">
+        <v>0</v>
+      </c>
+      <c r="BC24" s="19">
+        <v>0</v>
+      </c>
+      <c r="BE24" s="15"/>
+      <c r="BF24" s="15"/>
+      <c r="BG24" s="15"/>
+      <c r="BH24" s="15"/>
+      <c r="BI24" s="15"/>
+      <c r="BJ24" s="15"/>
+      <c r="BK24" s="15"/>
+      <c r="BL24" s="15"/>
+    </row>
+    <row r="25" spans="1:66" x14ac:dyDescent="0.35">
+      <c r="A25" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" s="19">
+        <v>0</v>
+      </c>
+      <c r="D25" s="19">
+        <v>1</v>
+      </c>
+      <c r="E25" s="19">
+        <v>5</v>
+      </c>
+      <c r="F25" s="19">
+        <v>24</v>
+      </c>
+      <c r="G25" s="19">
+        <v>2</v>
+      </c>
+      <c r="H25" s="19">
+        <v>17</v>
+      </c>
+      <c r="I25" s="19">
+        <v>9.3333333333333304</v>
+      </c>
+      <c r="J25" s="19">
+        <v>5.6666666666666599</v>
+      </c>
+      <c r="L25" s="19">
+        <v>0</v>
+      </c>
+      <c r="M25" s="19">
+        <v>0</v>
+      </c>
+      <c r="N25" s="19">
+        <v>0</v>
+      </c>
+      <c r="O25" s="19">
+        <v>0</v>
+      </c>
+      <c r="P25" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="19">
+        <v>0</v>
+      </c>
+      <c r="R25" s="19">
+        <v>0</v>
+      </c>
+      <c r="S25" s="19">
+        <v>0</v>
+      </c>
+      <c r="U25" s="19">
+        <v>0</v>
+      </c>
+      <c r="V25" s="19">
+        <v>0</v>
+      </c>
+      <c r="W25" s="19">
+        <v>0</v>
+      </c>
+      <c r="X25" s="19">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="19">
+        <v>4</v>
+      </c>
+      <c r="AE25" s="19">
+        <v>14</v>
+      </c>
+      <c r="AF25" s="19">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="19">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="19">
+        <v>16</v>
+      </c>
+      <c r="AJ25" s="19">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="19">
+        <v>2</v>
+      </c>
+      <c r="AM25" s="19">
+        <v>0</v>
+      </c>
+      <c r="AN25" s="19">
+        <v>0</v>
+      </c>
+      <c r="AO25" s="19">
+        <v>0</v>
+      </c>
+      <c r="AP25" s="19">
+        <v>0</v>
+      </c>
+      <c r="AQ25" s="19">
+        <v>0</v>
+      </c>
+      <c r="AR25" s="19">
+        <v>0</v>
+      </c>
+      <c r="AS25" s="19">
+        <v>0</v>
+      </c>
+      <c r="AT25" s="19">
+        <v>0</v>
+      </c>
+      <c r="AV25" s="19">
+        <v>0</v>
+      </c>
+      <c r="AW25" s="19">
+        <v>0</v>
+      </c>
+      <c r="AX25" s="19">
+        <v>0</v>
+      </c>
+      <c r="AY25" s="19">
+        <v>0</v>
+      </c>
+      <c r="AZ25" s="19">
+        <v>0</v>
+      </c>
+      <c r="BA25" s="19">
+        <v>0</v>
+      </c>
+      <c r="BB25" s="19">
+        <v>0</v>
+      </c>
+      <c r="BC25" s="19">
+        <v>0</v>
+      </c>
+      <c r="BE25" s="15">
+        <v>22.6</v>
+      </c>
+      <c r="BF25" s="15"/>
+      <c r="BG25" s="15"/>
+      <c r="BH25" s="15"/>
+      <c r="BI25" s="15"/>
+      <c r="BJ25" s="15"/>
+      <c r="BK25" s="15"/>
+      <c r="BL25" s="15"/>
+    </row>
+    <row r="26" spans="1:66" x14ac:dyDescent="0.35">
+      <c r="A26" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="L26" s="15"/>
+      <c r="M26" s="15"/>
+      <c r="N26" s="15"/>
+      <c r="O26" s="15">
+        <v>1</v>
+      </c>
+      <c r="P26" s="15"/>
+      <c r="Q26" s="15"/>
+      <c r="R26" s="15"/>
+      <c r="S26" s="15"/>
+      <c r="U26" s="15"/>
+      <c r="V26" s="15"/>
+      <c r="W26" s="15"/>
+      <c r="X26" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y26" s="15"/>
+      <c r="Z26" s="15"/>
+      <c r="AA26" s="15"/>
+      <c r="AB26" s="15"/>
+      <c r="AD26" s="15"/>
+      <c r="AE26" s="15"/>
+      <c r="AF26" s="15"/>
+      <c r="AG26" s="15">
+        <v>1</v>
+      </c>
+      <c r="AH26" s="15"/>
+      <c r="AI26" s="15"/>
+      <c r="AJ26" s="15"/>
+      <c r="AK26" s="15"/>
+      <c r="AM26" s="15"/>
+      <c r="AN26" s="15"/>
+      <c r="AO26" s="15"/>
+      <c r="AP26" s="15">
+        <v>1</v>
+      </c>
+      <c r="AQ26" s="15"/>
+      <c r="AR26" s="15"/>
+      <c r="AS26" s="15"/>
+      <c r="AT26" s="15"/>
+      <c r="AV26" s="15"/>
+      <c r="AW26" s="15"/>
+      <c r="AX26" s="15"/>
+      <c r="AY26" s="15">
+        <v>1</v>
+      </c>
+      <c r="AZ26" s="15"/>
+      <c r="BA26" s="15"/>
+      <c r="BB26" s="15"/>
+      <c r="BC26" s="15"/>
+      <c r="BE26" s="15"/>
+      <c r="BF26" s="15"/>
+      <c r="BG26" s="15"/>
+      <c r="BH26" s="15">
+        <v>1</v>
+      </c>
+      <c r="BI26" s="15"/>
+      <c r="BJ26" s="15"/>
+      <c r="BK26" s="15"/>
+      <c r="BL26" s="15"/>
+      <c r="BN26" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="27" spans="1:66" x14ac:dyDescent="0.35">
+      <c r="A27" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="L27" s="15">
+        <v>1</v>
+      </c>
+      <c r="M27" s="15"/>
+      <c r="N27" s="15"/>
+      <c r="O27" s="15"/>
+      <c r="P27" s="15"/>
+      <c r="Q27" s="15"/>
+      <c r="R27" s="15"/>
+      <c r="S27" s="15"/>
+      <c r="U27" s="15">
+        <v>1</v>
+      </c>
+      <c r="V27" s="15"/>
+      <c r="W27" s="15"/>
+      <c r="X27" s="15"/>
+      <c r="Y27" s="15"/>
+      <c r="Z27" s="15"/>
+      <c r="AA27" s="15"/>
+      <c r="AB27" s="15"/>
+      <c r="AD27" s="15">
+        <v>1</v>
+      </c>
+      <c r="AE27" s="15"/>
+      <c r="AF27" s="15"/>
+      <c r="AG27" s="15"/>
+      <c r="AH27" s="15"/>
+      <c r="AI27" s="15"/>
+      <c r="AJ27" s="15"/>
+      <c r="AK27" s="15"/>
+      <c r="AM27" s="15">
+        <v>1</v>
+      </c>
+      <c r="AN27" s="15"/>
+      <c r="AO27" s="15"/>
+      <c r="AP27" s="15"/>
+      <c r="AQ27" s="15"/>
+      <c r="AR27" s="15"/>
+      <c r="AS27" s="15"/>
+      <c r="AT27" s="15"/>
+      <c r="AV27" s="15">
+        <v>1</v>
+      </c>
+      <c r="AW27" s="15"/>
+      <c r="AX27" s="15"/>
+      <c r="AY27" s="15"/>
+      <c r="AZ27" s="15"/>
+      <c r="BA27" s="15"/>
+      <c r="BB27" s="15"/>
+      <c r="BC27" s="15"/>
+      <c r="BE27" s="15">
+        <v>1</v>
+      </c>
+      <c r="BF27" s="15"/>
+      <c r="BG27" s="15"/>
+      <c r="BH27" s="15"/>
+      <c r="BI27" s="15"/>
+      <c r="BJ27" s="15"/>
+      <c r="BK27" s="15"/>
+      <c r="BL27" s="15"/>
+      <c r="BN27" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="28" spans="1:66" x14ac:dyDescent="0.35">
+      <c r="A28" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F28" s="15">
+        <v>156.19919999999999</v>
+      </c>
+      <c r="H28" s="15">
+        <v>52.066400000000002</v>
+      </c>
+      <c r="I28" s="15">
+        <v>52.066400000000002</v>
+      </c>
+      <c r="L28" s="15"/>
+      <c r="M28" s="15"/>
+      <c r="N28" s="15"/>
+      <c r="O28" s="15"/>
+      <c r="P28" s="15"/>
+      <c r="Q28" s="15"/>
+      <c r="R28" s="15"/>
+      <c r="S28" s="15"/>
+      <c r="U28" s="15"/>
+      <c r="V28" s="15"/>
+      <c r="W28" s="15"/>
+      <c r="X28" s="15"/>
+      <c r="Y28" s="15"/>
+      <c r="AA28" s="15"/>
+      <c r="AB28" s="17">
+        <v>591.68500000000006</v>
+      </c>
+      <c r="AD28" s="15"/>
+      <c r="AE28" s="15">
+        <v>217.392</v>
+      </c>
+      <c r="AF28" s="15"/>
+      <c r="AG28" s="15"/>
+      <c r="AH28" s="15"/>
+      <c r="AI28" s="15"/>
+      <c r="AJ28" s="15"/>
+      <c r="AK28" s="15"/>
+      <c r="AM28" s="15"/>
+      <c r="AN28" s="15"/>
+      <c r="AO28" s="15"/>
+      <c r="AQ28" s="15"/>
+      <c r="AR28" s="15"/>
+      <c r="AS28" s="15"/>
+      <c r="AT28" s="15">
+        <v>20.681999999999999</v>
+      </c>
+      <c r="AV28" s="15"/>
+      <c r="AW28" s="15"/>
+      <c r="AX28" s="15"/>
+      <c r="AY28" s="15"/>
+      <c r="AZ28" s="15"/>
+      <c r="BA28" s="15"/>
+      <c r="BB28" s="15"/>
+      <c r="BC28" s="15"/>
+      <c r="BE28" s="15"/>
+      <c r="BF28" s="15"/>
+      <c r="BG28" s="15"/>
+      <c r="BH28" s="15"/>
+      <c r="BI28" s="15"/>
+      <c r="BJ28" s="15"/>
+      <c r="BK28" s="15"/>
+      <c r="BL28" s="15"/>
+      <c r="BN28" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" spans="1:66" x14ac:dyDescent="0.35">
+      <c r="A30" s="20" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" spans="1:66" x14ac:dyDescent="0.35">
+      <c r="A31" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="AB31" s="22" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32" spans="1:66" x14ac:dyDescent="0.35">
+      <c r="A32" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB32" s="22" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="33" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A33" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB33" s="23"/>
+    </row>
+    <row r="34" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AB34" s="22" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="35" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A35" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="AB35" s="22" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="36" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A36" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="AB36" s="22" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="37" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A37" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="AB37" s="22" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="38" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AB38" s="22" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="39" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A39" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="AB39" s="24"/>
+    </row>
+    <row r="40" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A40" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="41" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A41" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A42" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="43" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A43" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="44" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A44" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="45" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A45" s="25" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="46" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A46" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="47" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A47" s="5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A45" r:id="rId1" xr:uid="{EAEF6607-C569-460A-96A6-896D1D3DE224}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F73F2A9-DB39-4839-9475-3FC91EBA54C5}">
+  <dimension ref="B2:C27"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="42.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="C2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3">
+        <f>(SUMIFS('BPFUbIP-Summed Data by Industry'!C4:BL4,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Nonboiler heat")+SUMIFS('BPFUbIP-Summed Data by Industry'!C4:BL4,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Boilers"))/SUM('BPFUbIP-Summed Data by Industry'!C4:BL4)</f>
+        <v>0.31033233291513068</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4">
+        <f>(SUMIFS('BPFUbIP-Summed Data by Industry'!C5:BL5,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Nonboiler heat")+SUMIFS('BPFUbIP-Summed Data by Industry'!C5:BL5,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Boilers"))/SUM('BPFUbIP-Summed Data by Industry'!C5:BL5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5">
+        <f>(SUMIFS('BPFUbIP-Summed Data by Industry'!C6:BL6,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Nonboiler heat")+SUMIFS('BPFUbIP-Summed Data by Industry'!C6:BL6,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Boilers"))/SUM('BPFUbIP-Summed Data by Industry'!C6:BL6)</f>
+        <v>0.55501925030630439</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6">
+        <f>(SUMIFS('BPFUbIP-Summed Data by Industry'!C7:BL7,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Nonboiler heat")+SUMIFS('BPFUbIP-Summed Data by Industry'!C7:BL7,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Boilers"))/SUM('BPFUbIP-Summed Data by Industry'!C7:BL7)</f>
+        <v>0.47906040149384799</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7">
+        <f>(SUMIFS('BPFUbIP-Summed Data by Industry'!C8:BL8,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Nonboiler heat")+SUMIFS('BPFUbIP-Summed Data by Industry'!C8:BL8,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Boilers"))/SUM('BPFUbIP-Summed Data by Industry'!C8:BL8)</f>
+        <v>0.63987949274854616</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8">
+        <f>(SUMIFS('BPFUbIP-Summed Data by Industry'!C9:BL9,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Nonboiler heat")+SUMIFS('BPFUbIP-Summed Data by Industry'!C9:BL9,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Boilers"))/SUM('BPFUbIP-Summed Data by Industry'!C9:BL9)</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9">
+        <f>(SUMIFS('BPFUbIP-Summed Data by Industry'!C10:BL10,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Nonboiler heat")+SUMIFS('BPFUbIP-Summed Data by Industry'!C10:BL10,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Boilers"))/SUM('BPFUbIP-Summed Data by Industry'!C10:BL10)</f>
+        <v>0.86973788721207312</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10">
+        <f>(SUMIFS('BPFUbIP-Summed Data by Industry'!C11:BL11,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Nonboiler heat")+SUMIFS('BPFUbIP-Summed Data by Industry'!C11:BL11,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Boilers"))/SUM('BPFUbIP-Summed Data by Industry'!C11:BL11)</f>
+        <v>0.85513134401761959</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11">
+        <f>(SUMIFS('BPFUbIP-Summed Data by Industry'!C12:BL12,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Nonboiler heat")+SUMIFS('BPFUbIP-Summed Data by Industry'!C12:BL12,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Boilers"))/SUM('BPFUbIP-Summed Data by Industry'!C12:BL12)</f>
+        <v>0.77536793183578623</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12">
+        <f>(SUMIFS('BPFUbIP-Summed Data by Industry'!C13:BL13,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Nonboiler heat")+SUMIFS('BPFUbIP-Summed Data by Industry'!C13:BL13,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Boilers"))/SUM('BPFUbIP-Summed Data by Industry'!C13:BL13)</f>
+        <v>0.71612700408676522</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13">
+        <f>(SUMIFS('BPFUbIP-Summed Data by Industry'!C14:BL14,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Nonboiler heat")+SUMIFS('BPFUbIP-Summed Data by Industry'!C14:BL14,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Boilers"))/SUM('BPFUbIP-Summed Data by Industry'!C14:BL14)</f>
+        <v>0.28205128205128205</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14">
+        <f>(SUMIFS('BPFUbIP-Summed Data by Industry'!C15:BL15,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Nonboiler heat")+SUMIFS('BPFUbIP-Summed Data by Industry'!C15:BL15,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Boilers"))/SUM('BPFUbIP-Summed Data by Industry'!C15:BL15)</f>
+        <v>0.75135135135135134</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15">
+        <f>(SUMIFS('BPFUbIP-Summed Data by Industry'!C16:BL16,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Nonboiler heat")+SUMIFS('BPFUbIP-Summed Data by Industry'!C16:BL16,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Boilers"))/SUM('BPFUbIP-Summed Data by Industry'!C16:BL16)</f>
+        <v>0.84923168466505305</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16">
+        <f>(SUMIFS('BPFUbIP-Summed Data by Industry'!C17:BL17,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Nonboiler heat")+SUMIFS('BPFUbIP-Summed Data by Industry'!C17:BL17,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Boilers"))/SUM('BPFUbIP-Summed Data by Industry'!C17:BL17)</f>
+        <v>0.65160349854227417</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17">
+        <f>(SUMIFS('BPFUbIP-Summed Data by Industry'!C18:BL18,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Nonboiler heat")+SUMIFS('BPFUbIP-Summed Data by Industry'!C18:BL18,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Boilers"))/SUM('BPFUbIP-Summed Data by Industry'!C18:BL18)</f>
+        <v>0.60889929742388771</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B18" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18">
+        <f>(SUMIFS('BPFUbIP-Summed Data by Industry'!C19:BL19,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Nonboiler heat")+SUMIFS('BPFUbIP-Summed Data by Industry'!C19:BL19,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Boilers"))/SUM('BPFUbIP-Summed Data by Industry'!C19:BL19)</f>
+        <v>0.58726415094339623</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B19" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19">
+        <f>(SUMIFS('BPFUbIP-Summed Data by Industry'!C20:BL20,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Nonboiler heat")+SUMIFS('BPFUbIP-Summed Data by Industry'!C20:BL20,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Boilers"))/SUM('BPFUbIP-Summed Data by Industry'!C20:BL20)</f>
+        <v>0.15079365079365079</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B20" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20">
+        <f>(SUMIFS('BPFUbIP-Summed Data by Industry'!C21:BL21,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Nonboiler heat")+SUMIFS('BPFUbIP-Summed Data by Industry'!C21:BL21,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Boilers"))/SUM('BPFUbIP-Summed Data by Industry'!C21:BL21)</f>
+        <v>0.34210526315789475</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B21" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21">
+        <f>(SUMIFS('BPFUbIP-Summed Data by Industry'!C22:BL22,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Nonboiler heat")+SUMIFS('BPFUbIP-Summed Data by Industry'!C22:BL22,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Boilers"))/SUM('BPFUbIP-Summed Data by Industry'!C22:BL22)</f>
+        <v>0.21830985915492956</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22">
+        <f>(SUMIFS('BPFUbIP-Summed Data by Industry'!C23:BL23,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Nonboiler heat")+SUMIFS('BPFUbIP-Summed Data by Industry'!C23:BL23,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Boilers"))/SUM('BPFUbIP-Summed Data by Industry'!C23:BL23)</f>
+        <v>0.44776119402985076</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B23" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23">
+        <f>(SUMIFS('BPFUbIP-Summed Data by Industry'!C24:BL24,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Nonboiler heat")+SUMIFS('BPFUbIP-Summed Data by Industry'!C24:BL24,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Boilers"))/SUM('BPFUbIP-Summed Data by Industry'!C24:BL24)</f>
+        <v>0.32758620689655171</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B24" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24">
+        <f>(SUMIFS('BPFUbIP-Summed Data by Industry'!C25:BL25,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Nonboiler heat")+SUMIFS('BPFUbIP-Summed Data by Industry'!C25:BL25,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Boilers"))/SUM('BPFUbIP-Summed Data by Industry'!C25:BL25)</f>
+        <v>0.33931484502446985</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B25" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25">
+        <f>(SUMIFS('BPFUbIP-Summed Data by Industry'!C26:BL26,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Nonboiler heat")+SUMIFS('BPFUbIP-Summed Data by Industry'!C26:BL26,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Boilers"))/SUM('BPFUbIP-Summed Data by Industry'!C26:BL26)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26">
+        <f>(SUMIFS('BPFUbIP-Summed Data by Industry'!C27:BL27,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Nonboiler heat")+SUMIFS('BPFUbIP-Summed Data by Industry'!C27:BL27,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Boilers"))/SUM('BPFUbIP-Summed Data by Industry'!C27:BL27)</f>
+        <v>0.8571428571428571</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B27" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27">
+        <f>(SUMIFS('BPFUbIP-Summed Data by Industry'!C28:BL28,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Nonboiler heat")+SUMIFS('BPFUbIP-Summed Data by Industry'!C28:BL28,'BPFUbIP-Summed Data by Industry'!$C$3:$BL$3,"Boilers"))/SUM('BPFUbIP-Summed Data by Industry'!C28:BL28)</f>
+        <v>0.19942555254561314</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15C4D4F2-9192-4557-9476-0BAD41DB5078}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="45.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="45.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>53</v>
       </c>
@@ -1976,232 +6942,244 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>26</v>
       </c>
       <c r="B2" s="8">
-        <f>SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A2)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A2)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR((SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A2)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A2)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A2))/Calcs!$C3,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>27</v>
       </c>
       <c r="B3" s="8">
-        <f>SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A3)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A3)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A3)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR((SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A3)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A3)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A3))/Calcs!$C4,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>28</v>
       </c>
       <c r="B4" s="8">
-        <f>SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A4)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A4)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A4)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR((SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A4)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A4)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A4))/Calcs!$C5,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>29</v>
       </c>
       <c r="B5" s="8">
-        <f>SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A5)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A5)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A5)</f>
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR((SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A5)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A5)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A5))/Calcs!$C6,0)</f>
+        <v>1.0437097252055405E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>30</v>
       </c>
       <c r="B6" s="8">
-        <f>SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A6)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A6)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A6)</f>
-        <v>5.8999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR((SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A6)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A6)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A6))/Calcs!$C7,0)</f>
+        <v>9.2204861491295309E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>31</v>
       </c>
       <c r="B7" s="8">
-        <f>SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A7)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A7)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A7)</f>
-        <v>8.9999999999999993E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR((SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A7)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A7)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A7))/Calcs!$C8,0)</f>
+        <v>2.2499999999999996E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>32</v>
       </c>
       <c r="B8" s="8">
-        <f>SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A8)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A8)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A8)</f>
-        <v>8.0000000000000002E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR((SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A8)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A8)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A8))/Calcs!$C9,0)</f>
+        <v>9.1981735159817352E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>33</v>
       </c>
       <c r="B9" s="8">
-        <f>SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A9)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A9)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A9)</f>
-        <v>4.4999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR((SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A9)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A9)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A9))/Calcs!$C10,0)</f>
+        <v>5.2623494992685933E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>34</v>
       </c>
       <c r="B10" s="8">
-        <f>SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A10)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A10)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A10)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR((SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A10)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A10)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A10))/Calcs!$C11,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>35</v>
       </c>
       <c r="B11" s="8">
-        <f>SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A11)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A11)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A11)</f>
-        <v>5.7000000000000002E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR((SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A11)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A11)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A11))/Calcs!$C12,0)</f>
+        <v>7.9594820017559256E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>36</v>
       </c>
       <c r="B12" s="8">
-        <f>SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A12)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A12)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A12)</f>
-        <v>3.3000000000000002E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR((SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A12)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A12)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A12))/Calcs!$C13,0)</f>
+        <v>0.11700000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>37</v>
       </c>
       <c r="B13" s="8">
-        <f>SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A13)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A13)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A13)</f>
-        <v>7.3999999999999996E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR((SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A13)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A13)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A13))/Calcs!$C14,0)</f>
+        <v>9.8489208633093517E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>38</v>
       </c>
       <c r="B14" s="8">
-        <f>SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A14)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A14)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A14)</f>
-        <v>7.3999999999999996E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR((SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A14)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A14)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A14))/Calcs!$C15,0)</f>
+        <v>8.7137587228844932E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>39</v>
       </c>
       <c r="B15" s="8">
-        <f>SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A15)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A15)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A15)</f>
-        <v>9.0999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR((SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A15)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A15)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A15))/Calcs!$C16,0)</f>
+        <v>0.13965548098434002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>40</v>
       </c>
       <c r="B16" s="8">
-        <f>SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A16)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A16)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A16)</f>
-        <v>2.4E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR((SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A16)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A16)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A16))/Calcs!$C17,0)</f>
+        <v>3.9415384615384609E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>41</v>
       </c>
       <c r="B17" s="8">
-        <f>SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A17)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A17)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A17)</f>
-        <v>3.3000000000000002E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR((SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A17)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A17)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A17))/Calcs!$C18,0)</f>
+        <v>5.6192771084337352E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>42</v>
       </c>
       <c r="B18" s="8">
-        <f>SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A18)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A18)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A18)</f>
-        <v>3.3000000000000002E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR((SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A18)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A18)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A18))/Calcs!$C19,0)</f>
+        <v>0.21884210526315792</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>43</v>
       </c>
       <c r="B19" s="8">
-        <f>SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A19)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A19)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A19)</f>
-        <v>3.3000000000000002E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR((SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A19)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A19)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A19))/Calcs!$C20,0)</f>
+        <v>9.646153846153846E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>44</v>
       </c>
       <c r="B20" s="8">
-        <f>SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A20)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A20)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A20)</f>
-        <v>3.3000000000000002E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR((SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A20)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A20)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A20))/Calcs!$C21,0)</f>
+        <v>0.15116129032258066</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>45</v>
       </c>
       <c r="B21" s="8">
-        <f>SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A21)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A21)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A21)</f>
-        <v>1.2999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR((SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A21)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A21)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A21))/Calcs!$C22,0)</f>
+        <v>2.9033333333333331E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>46</v>
       </c>
       <c r="B22" s="8">
-        <f>SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A22)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A22)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A22)</f>
-        <v>1.2999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR((SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A22)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A22)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A22))/Calcs!$C23,0)</f>
+        <v>3.9684210526315787E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>47</v>
       </c>
       <c r="B23" s="8">
-        <f>SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A23)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A23)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A23)</f>
-        <v>3.3000000000000002E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR((SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A23)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A23)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A23))/Calcs!$C24,0)</f>
+        <v>9.7254807692307696E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>48</v>
       </c>
       <c r="B24" s="8">
-        <f>SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A24)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A24)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A24)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR((SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A24)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A24)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A24))/Calcs!$C25,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>49</v>
       </c>
       <c r="B25" s="8">
-        <f>SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A25)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A25)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A25)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+        <f>IFERROR((SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A25)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A25)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A25))/Calcs!$C26,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>50</v>
       </c>
       <c r="B26" s="8">
-        <f>SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A26)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A26)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A26)</f>
-        <v>1.6E-2</v>
+        <f>IFERROR((SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$H$23:$H$35,WHRPbI!A26)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$I$23:$I$35,WHRPbI!A26)+SUMIFS('EU Data'!$D$23:$D$35,'EU Data'!$J$23:$J$35,WHRPbI!A26))/Calcs!$C27,0)</f>
+        <v>8.023044086258925E-2</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:B26">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>